--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -113,9 +113,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -490,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46484</v>
+        <v>46470</v>
       </c>
       <c r="C2" t="n">
-        <v>47268</v>
+        <v>46778</v>
       </c>
       <c r="D2" t="n">
-        <v>46200</v>
+        <v>45712</v>
       </c>
       <c r="E2" t="n">
-        <v>47201</v>
+        <v>46036</v>
       </c>
       <c r="F2" t="n">
-        <v>844</v>
+        <v>1016</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0182</v>
+        <v>0.0226</v>
       </c>
       <c r="H2" t="n">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="I2" t="n">
-        <v>41712</v>
+        <v>43919</v>
       </c>
       <c r="J2" t="n">
-        <v>44420</v>
+        <v>43808.25</v>
       </c>
       <c r="K2" t="n">
-        <v>45140</v>
+        <v>44516.5</v>
       </c>
       <c r="L2" t="n">
-        <v>45860</v>
+        <v>45224.75</v>
       </c>
       <c r="M2" t="n">
-        <v>47574</v>
+        <v>45523.5</v>
       </c>
       <c r="N2" t="n">
-        <v>49288</v>
+        <v>45822.25</v>
       </c>
       <c r="O2" t="n">
-        <v>49014</v>
+        <v>46940</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -705,14 +702,18 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="9" t="inlineStr"/>
-      <c r="W2" s="10" t="inlineStr">
+      <c r="V2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -722,134 +723,134 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47278</v>
+        <v>47460</v>
       </c>
       <c r="C3" t="n">
-        <v>47519</v>
+        <v>48476</v>
       </c>
       <c r="D3" t="n">
-        <v>46043</v>
+        <v>46729</v>
       </c>
       <c r="E3" t="n">
-        <v>46165</v>
+        <v>47565</v>
       </c>
       <c r="F3" t="n">
-        <v>-1036</v>
+        <v>1529</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0219</v>
+        <v>0.0332</v>
       </c>
       <c r="H3" t="n">
-        <v>1476</v>
+        <v>1747</v>
       </c>
       <c r="I3" t="n">
-        <v>45132</v>
+        <v>44646</v>
       </c>
       <c r="J3" t="n">
-        <v>46366.5</v>
+        <v>44865.5</v>
       </c>
       <c r="K3" t="n">
-        <v>46667</v>
+        <v>45503</v>
       </c>
       <c r="L3" t="n">
-        <v>46967.5</v>
+        <v>46140.5</v>
       </c>
       <c r="M3" t="n">
-        <v>47735</v>
+        <v>46569</v>
       </c>
       <c r="N3" t="n">
-        <v>48502.5</v>
+        <v>46997.5</v>
       </c>
       <c r="O3" t="n">
-        <v>48336</v>
+        <v>47844</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="11" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="9" t="inlineStr"/>
-      <c r="W3" s="12" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46188</v>
+        <v>48650</v>
       </c>
       <c r="C4" t="n">
-        <v>46512</v>
+        <v>49240</v>
       </c>
       <c r="D4" t="n">
-        <v>45646</v>
+        <v>47404</v>
       </c>
       <c r="E4" t="n">
-        <v>45819</v>
+        <v>48883</v>
       </c>
       <c r="F4" t="n">
-        <v>-346</v>
+        <v>1318</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.0277</v>
       </c>
       <c r="H4" t="n">
-        <v>866</v>
+        <v>1836</v>
       </c>
       <c r="I4" t="n">
-        <v>44567</v>
+        <v>44982</v>
       </c>
       <c r="J4" t="n">
-        <v>44381</v>
+        <v>45799.25</v>
       </c>
       <c r="K4" t="n">
-        <v>45427</v>
+        <v>46691.5</v>
       </c>
       <c r="L4" t="n">
-        <v>46473</v>
+        <v>47583.75</v>
       </c>
       <c r="M4" t="n">
-        <v>46903</v>
+        <v>48438.5</v>
       </c>
       <c r="N4" t="n">
-        <v>47333</v>
+        <v>49293.25</v>
       </c>
       <c r="O4" t="n">
-        <v>48995</v>
+        <v>50223</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -857,26 +858,30 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="9" t="inlineStr"/>
-      <c r="W4" s="12" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -884,134 +889,134 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45951</v>
+        <v>46858</v>
       </c>
       <c r="C5" t="n">
-        <v>46817</v>
+        <v>47072</v>
       </c>
       <c r="D5" t="n">
-        <v>45415</v>
+        <v>45898</v>
       </c>
       <c r="E5" t="n">
-        <v>46709</v>
+        <v>46207</v>
       </c>
       <c r="F5" t="n">
-        <v>890</v>
+        <v>-2676</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0194</v>
+        <v>-0.0547</v>
       </c>
       <c r="H5" t="n">
-        <v>1402</v>
+        <v>1174</v>
       </c>
       <c r="I5" t="n">
-        <v>44780</v>
+        <v>45568</v>
       </c>
       <c r="J5" t="n">
-        <v>44823</v>
+        <v>47327.5</v>
       </c>
       <c r="K5" t="n">
-        <v>45386</v>
+        <v>47965</v>
       </c>
       <c r="L5" t="n">
-        <v>45949</v>
+        <v>48602.5</v>
       </c>
       <c r="M5" t="n">
-        <v>46252</v>
+        <v>49801</v>
       </c>
       <c r="N5" t="n">
-        <v>46555</v>
+        <v>50999.5</v>
       </c>
       <c r="O5" t="n">
-        <v>47378</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
+        <v>51076</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V5" s="9" t="inlineStr"/>
-      <c r="W5" s="10" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47280</v>
+        <v>46993</v>
       </c>
       <c r="C6" t="n">
-        <v>47572</v>
+        <v>46997</v>
       </c>
       <c r="D6" t="n">
-        <v>47093</v>
+        <v>45063</v>
       </c>
       <c r="E6" t="n">
-        <v>47329</v>
+        <v>46910</v>
       </c>
       <c r="F6" t="n">
-        <v>620</v>
+        <v>703</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0152</v>
       </c>
       <c r="H6" t="n">
-        <v>479</v>
+        <v>1934</v>
       </c>
       <c r="I6" t="n">
-        <v>44013</v>
+        <v>44724</v>
       </c>
       <c r="J6" t="n">
-        <v>45603.5</v>
+        <v>44894</v>
       </c>
       <c r="K6" t="n">
-        <v>46008</v>
+        <v>45620</v>
       </c>
       <c r="L6" t="n">
-        <v>46412.5</v>
+        <v>46346</v>
       </c>
       <c r="M6" t="n">
-        <v>47410</v>
+        <v>46794</v>
       </c>
       <c r="N6" t="n">
-        <v>48407.5</v>
+        <v>47242</v>
       </c>
       <c r="O6" t="n">
-        <v>48219</v>
+        <v>48246</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,8 +1024,10 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
@@ -1035,66 +1042,70 @@
       <c r="U6" s="8" t="n">
         <v/>
       </c>
-      <c r="V6" s="9" t="inlineStr"/>
-      <c r="W6" s="10" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47480</v>
+        <v>45709</v>
       </c>
       <c r="C7" t="n">
-        <v>47593</v>
+        <v>46884</v>
       </c>
       <c r="D7" t="n">
-        <v>46561</v>
+        <v>44264</v>
       </c>
       <c r="E7" t="n">
-        <v>47055</v>
+        <v>45805</v>
       </c>
       <c r="F7" t="n">
-        <v>-274</v>
+        <v>-1105</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0058</v>
+        <v>-0.0236</v>
       </c>
       <c r="H7" t="n">
-        <v>1032</v>
+        <v>2620</v>
       </c>
       <c r="I7" t="n">
-        <v>46614</v>
+        <v>43129</v>
       </c>
       <c r="J7" t="n">
-        <v>46848.25</v>
+        <v>45416</v>
       </c>
       <c r="K7" t="n">
-        <v>47089.5</v>
+        <v>45943</v>
       </c>
       <c r="L7" t="n">
-        <v>47330.75</v>
+        <v>46470</v>
       </c>
       <c r="M7" t="n">
-        <v>47568.5</v>
+        <v>47877</v>
       </c>
       <c r="N7" t="n">
-        <v>47806.25</v>
+        <v>49284</v>
       </c>
       <c r="O7" t="n">
-        <v>48051</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>48931</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
@@ -1106,78 +1117,74 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="11" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
-      <c r="V7" s="9" t="inlineStr"/>
-      <c r="W7" s="10" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47076</v>
+        <v>44799</v>
       </c>
       <c r="C8" t="n">
-        <v>47592</v>
+        <v>45637</v>
       </c>
       <c r="D8" t="n">
-        <v>46747</v>
+        <v>44135</v>
       </c>
       <c r="E8" t="n">
-        <v>46984</v>
+        <v>44995</v>
       </c>
       <c r="F8" t="n">
-        <v>-71</v>
+        <v>-810</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0177</v>
       </c>
       <c r="H8" t="n">
-        <v>845</v>
+        <v>1502</v>
       </c>
       <c r="I8" t="n">
-        <v>45529</v>
+        <v>41644</v>
       </c>
       <c r="J8" t="n">
-        <v>46012</v>
+        <v>43300.5</v>
       </c>
       <c r="K8" t="n">
-        <v>46539</v>
+        <v>44495</v>
       </c>
       <c r="L8" t="n">
-        <v>47066</v>
+        <v>45689.5</v>
       </c>
       <c r="M8" t="n">
-        <v>47571</v>
+        <v>47115</v>
       </c>
       <c r="N8" t="n">
-        <v>48076</v>
+        <v>48540.5</v>
       </c>
       <c r="O8" t="n">
-        <v>48625</v>
+        <v>49504</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,144 +1192,4740 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="11" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
-      <c r="V8" s="9" t="inlineStr"/>
-      <c r="W8" s="10" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>46100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>46883</v>
+      </c>
+      <c r="D9" t="n">
+        <v>45038</v>
+      </c>
+      <c r="E9" t="n">
+        <v>46361</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1366</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.0304</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1845</v>
+      </c>
+      <c r="I9" t="n">
+        <v>42633</v>
+      </c>
+      <c r="J9" t="n">
+        <v>43547.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>44244</v>
+      </c>
+      <c r="L9" t="n">
+        <v>44940.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>45746</v>
+      </c>
+      <c r="N9" t="n">
+        <v>46551.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>47139</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>47516</v>
+      </c>
+      <c r="C10" t="n">
+        <v>47695</v>
+      </c>
+      <c r="D10" t="n">
+        <v>46365</v>
+      </c>
+      <c r="E10" t="n">
+        <v>47428</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1067</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1330</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43193</v>
+      </c>
+      <c r="J10" t="n">
+        <v>44716.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>45438.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>46160.75</v>
+      </c>
+      <c r="M10" t="n">
+        <v>47283.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>48406.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>48728</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C11" t="n">
+        <v>47548</v>
+      </c>
+      <c r="D11" t="n">
+        <v>45780</v>
+      </c>
+      <c r="E11" t="n">
+        <v>46354</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1074</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.0226</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1768</v>
+      </c>
+      <c r="I11" t="n">
+        <v>45035</v>
+      </c>
+      <c r="J11" t="n">
+        <v>46297</v>
+      </c>
+      <c r="K11" t="n">
+        <v>46763</v>
+      </c>
+      <c r="L11" t="n">
+        <v>47229</v>
+      </c>
+      <c r="M11" t="n">
+        <v>48093</v>
+      </c>
+      <c r="N11" t="n">
+        <v>48957</v>
+      </c>
+      <c r="O11" t="n">
+        <v>49025</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>45700</v>
+      </c>
+      <c r="C12" t="n">
+        <v>47223</v>
+      </c>
+      <c r="D12" t="n">
+        <v>45271</v>
+      </c>
+      <c r="E12" t="n">
+        <v>45668</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-686</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-0.0148</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1952</v>
+      </c>
+      <c r="I12" t="n">
+        <v>44012</v>
+      </c>
+      <c r="J12" t="n">
+        <v>44431</v>
+      </c>
+      <c r="K12" t="n">
+        <v>45470</v>
+      </c>
+      <c r="L12" t="n">
+        <v>46509</v>
+      </c>
+      <c r="M12" t="n">
+        <v>47238</v>
+      </c>
+      <c r="N12" t="n">
+        <v>47967</v>
+      </c>
+      <c r="O12" t="n">
+        <v>49316</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>47280</v>
+      </c>
+      <c r="C13" t="n">
+        <v>47547</v>
+      </c>
+      <c r="D13" t="n">
+        <v>46531</v>
+      </c>
+      <c r="E13" t="n">
+        <v>47116</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1448</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1016</v>
+      </c>
+      <c r="I13" t="n">
+        <v>43319</v>
+      </c>
+      <c r="J13" t="n">
+        <v>43426.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>44692</v>
+      </c>
+      <c r="L13" t="n">
+        <v>45957.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>46644</v>
+      </c>
+      <c r="N13" t="n">
+        <v>47330.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>49175</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>47000</v>
+      </c>
+      <c r="C14" t="n">
+        <v>47500</v>
+      </c>
+      <c r="D14" t="n">
+        <v>45599</v>
+      </c>
+      <c r="E14" t="n">
+        <v>47340</v>
+      </c>
+      <c r="F14" t="n">
+        <v>224</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1901</v>
+      </c>
+      <c r="I14" t="n">
+        <v>45515</v>
+      </c>
+      <c r="J14" t="n">
+        <v>46138.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>46608</v>
+      </c>
+      <c r="L14" t="n">
+        <v>47077.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>47624</v>
+      </c>
+      <c r="N14" t="n">
+        <v>48170.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>48563</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>45606</v>
+      </c>
+      <c r="C15" t="n">
+        <v>46003</v>
+      </c>
+      <c r="D15" t="n">
+        <v>44904</v>
+      </c>
+      <c r="E15" t="n">
+        <v>45207</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-2133</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>-0.0451</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1099</v>
+      </c>
+      <c r="I15" t="n">
+        <v>43698</v>
+      </c>
+      <c r="J15" t="n">
+        <v>45834.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>46389.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>46944.75</v>
+      </c>
+      <c r="M15" t="n">
+        <v>48290.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>49636.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>49401</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>46008</v>
+      </c>
+      <c r="C16" t="n">
+        <v>46158</v>
+      </c>
+      <c r="D16" t="n">
+        <v>44575</v>
+      </c>
+      <c r="E16" t="n">
+        <v>45727</v>
+      </c>
+      <c r="F16" t="n">
+        <v>520</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1583</v>
+      </c>
+      <c r="I16" t="n">
+        <v>43805</v>
+      </c>
+      <c r="J16" t="n">
+        <v>43984.75</v>
+      </c>
+      <c r="K16" t="n">
+        <v>44657.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>45330.25</v>
+      </c>
+      <c r="M16" t="n">
+        <v>45756.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>46182.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>47102</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>46222</v>
+      </c>
+      <c r="C17" t="n">
+        <v>46495</v>
+      </c>
+      <c r="D17" t="n">
+        <v>45251</v>
+      </c>
+      <c r="E17" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="n">
+        <v>554</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1244</v>
+      </c>
+      <c r="I17" t="n">
+        <v>42992</v>
+      </c>
+      <c r="J17" t="n">
+        <v>44324.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>44935.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>45546.75</v>
+      </c>
+      <c r="M17" t="n">
+        <v>46518.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>47490.25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>47741</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>45046</v>
+      </c>
+      <c r="C18" t="n">
+        <v>45888</v>
+      </c>
+      <c r="D18" t="n">
+        <v>43852</v>
+      </c>
+      <c r="E18" t="n">
+        <v>45058</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1223</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-0.0264</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2036</v>
+      </c>
+      <c r="I18" t="n">
+        <v>44007</v>
+      </c>
+      <c r="J18" t="n">
+        <v>45241</v>
+      </c>
+      <c r="K18" t="n">
+        <v>45659</v>
+      </c>
+      <c r="L18" t="n">
+        <v>46077</v>
+      </c>
+      <c r="M18" t="n">
+        <v>46903</v>
+      </c>
+      <c r="N18" t="n">
+        <v>47729</v>
+      </c>
+      <c r="O18" t="n">
+        <v>47739</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>45353</v>
+      </c>
+      <c r="C19" t="n">
+        <v>45842</v>
+      </c>
+      <c r="D19" t="n">
+        <v>44648</v>
+      </c>
+      <c r="E19" t="n">
+        <v>45015</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-43</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1194</v>
+      </c>
+      <c r="I19" t="n">
+        <v>41816</v>
+      </c>
+      <c r="J19" t="n">
+        <v>43116</v>
+      </c>
+      <c r="K19" t="n">
+        <v>44040</v>
+      </c>
+      <c r="L19" t="n">
+        <v>44964</v>
+      </c>
+      <c r="M19" t="n">
+        <v>46076</v>
+      </c>
+      <c r="N19" t="n">
+        <v>47188</v>
+      </c>
+      <c r="O19" t="n">
+        <v>47924</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>45519</v>
+      </c>
+      <c r="C20" t="n">
+        <v>46260</v>
+      </c>
+      <c r="D20" t="n">
+        <v>45191</v>
+      </c>
+      <c r="E20" t="n">
+        <v>45817</v>
+      </c>
+      <c r="F20" t="n">
+        <v>802</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1069</v>
+      </c>
+      <c r="I20" t="n">
+        <v>43454</v>
+      </c>
+      <c r="J20" t="n">
+        <v>43706</v>
+      </c>
+      <c r="K20" t="n">
+        <v>44418</v>
+      </c>
+      <c r="L20" t="n">
+        <v>45130</v>
+      </c>
+      <c r="M20" t="n">
+        <v>45612</v>
+      </c>
+      <c r="N20" t="n">
+        <v>46094</v>
+      </c>
+      <c r="O20" t="n">
+        <v>47036</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>44250</v>
+      </c>
+      <c r="C21" t="n">
+        <v>45450</v>
+      </c>
+      <c r="D21" t="n">
+        <v>42527</v>
+      </c>
+      <c r="E21" t="n">
+        <v>44715</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-1102</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2923</v>
+      </c>
+      <c r="I21" t="n">
+        <v>44122</v>
+      </c>
+      <c r="J21" t="n">
+        <v>44793.75</v>
+      </c>
+      <c r="K21" t="n">
+        <v>45282.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>45771.25</v>
+      </c>
+      <c r="M21" t="n">
+        <v>46351.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>46931.75</v>
+      </c>
+      <c r="O21" t="n">
+        <v>47329</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>43500</v>
+      </c>
+      <c r="C22" t="n">
+        <v>43771</v>
+      </c>
+      <c r="D22" t="n">
+        <v>42173</v>
+      </c>
+      <c r="E22" t="n">
+        <v>43481</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1234</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.0276</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1598</v>
+      </c>
+      <c r="I22" t="n">
+        <v>39604</v>
+      </c>
+      <c r="J22" t="n">
+        <v>42155.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>43253.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>44351.75</v>
+      </c>
+      <c r="M22" t="n">
+        <v>46176.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>48001.25</v>
+      </c>
+      <c r="O22" t="n">
+        <v>48373</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>43297</v>
+      </c>
+      <c r="C23" t="n">
+        <v>44404</v>
+      </c>
+      <c r="D23" t="n">
+        <v>42640</v>
+      </c>
+      <c r="E23" t="n">
+        <v>42979</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-502</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1764</v>
+      </c>
+      <c r="I23" t="n">
+        <v>40575</v>
+      </c>
+      <c r="J23" t="n">
+        <v>42137.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>42682</v>
+      </c>
+      <c r="L23" t="n">
+        <v>43226.5</v>
+      </c>
+      <c r="M23" t="n">
+        <v>44280</v>
+      </c>
+      <c r="N23" t="n">
+        <v>45333.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>45369</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>45000</v>
+      </c>
+      <c r="C24" t="n">
+        <v>45364</v>
+      </c>
+      <c r="D24" t="n">
+        <v>44414</v>
+      </c>
+      <c r="E24" t="n">
+        <v>44961</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1982</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="H24" t="n">
+        <v>950</v>
+      </c>
+      <c r="I24" t="n">
+        <v>40876</v>
+      </c>
+      <c r="J24" t="n">
+        <v>40943.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>42097</v>
+      </c>
+      <c r="L24" t="n">
+        <v>43250.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>43861</v>
+      </c>
+      <c r="N24" t="n">
+        <v>44471.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>46168</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>45310</v>
+      </c>
+      <c r="C25" t="n">
+        <v>45339</v>
+      </c>
+      <c r="D25" t="n">
+        <v>44395</v>
+      </c>
+      <c r="E25" t="n">
+        <v>45034</v>
+      </c>
+      <c r="F25" t="n">
+        <v>73</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="H25" t="n">
+        <v>944</v>
+      </c>
+      <c r="I25" t="n">
+        <v>43464</v>
+      </c>
+      <c r="J25" t="n">
+        <v>44047</v>
+      </c>
+      <c r="K25" t="n">
+        <v>44486</v>
+      </c>
+      <c r="L25" t="n">
+        <v>44925</v>
+      </c>
+      <c r="M25" t="n">
+        <v>45436</v>
+      </c>
+      <c r="N25" t="n">
+        <v>45947</v>
+      </c>
+      <c r="O25" t="n">
+        <v>46314</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>44166</v>
+      </c>
+      <c r="C26" t="n">
+        <v>45028</v>
+      </c>
+      <c r="D26" t="n">
+        <v>43640</v>
+      </c>
+      <c r="E26" t="n">
+        <v>44391</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-643</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1388</v>
+      </c>
+      <c r="I26" t="n">
+        <v>43451</v>
+      </c>
+      <c r="J26" t="n">
+        <v>44173.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>44562</v>
+      </c>
+      <c r="L26" t="n">
+        <v>44950.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>45506</v>
+      </c>
+      <c r="N26" t="n">
+        <v>46061.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>46283</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>43888</v>
+      </c>
+      <c r="C27" t="n">
+        <v>44306</v>
+      </c>
+      <c r="D27" t="n">
+        <v>43176</v>
+      </c>
+      <c r="E27" t="n">
+        <v>43369</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1022</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1130</v>
+      </c>
+      <c r="I27" t="n">
+        <v>42252</v>
+      </c>
+      <c r="J27" t="n">
+        <v>43031.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>43697</v>
+      </c>
+      <c r="L27" t="n">
+        <v>44362.5</v>
+      </c>
+      <c r="M27" t="n">
+        <v>45085</v>
+      </c>
+      <c r="N27" t="n">
+        <v>45807.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>46416</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>42569</v>
+      </c>
+      <c r="C28" t="n">
+        <v>44241</v>
+      </c>
+      <c r="D28" t="n">
+        <v>41516</v>
+      </c>
+      <c r="E28" t="n">
+        <v>43172</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-197</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.0045</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2725</v>
+      </c>
+      <c r="I28" t="n">
+        <v>42046</v>
+      </c>
+      <c r="J28" t="n">
+        <v>42053</v>
+      </c>
+      <c r="K28" t="n">
+        <v>42804</v>
+      </c>
+      <c r="L28" t="n">
+        <v>43555</v>
+      </c>
+      <c r="M28" t="n">
+        <v>43934</v>
+      </c>
+      <c r="N28" t="n">
+        <v>44313</v>
+      </c>
+      <c r="O28" t="n">
+        <v>45436</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>41915</v>
+      </c>
+      <c r="C29" t="n">
+        <v>42108</v>
+      </c>
+      <c r="D29" t="n">
+        <v>39442</v>
+      </c>
+      <c r="E29" t="n">
+        <v>41889</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1283</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-0.0297</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2666</v>
+      </c>
+      <c r="I29" t="n">
+        <v>38791</v>
+      </c>
+      <c r="J29" t="n">
+        <v>40593.75</v>
+      </c>
+      <c r="K29" t="n">
+        <v>41809.5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>43025.25</v>
+      </c>
+      <c r="M29" t="n">
+        <v>44534.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>46043.75</v>
+      </c>
+      <c r="O29" t="n">
+        <v>46966</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>40007</v>
+      </c>
+      <c r="C30" t="n">
+        <v>41266</v>
+      </c>
+      <c r="D30" t="n">
+        <v>39447</v>
+      </c>
+      <c r="E30" t="n">
+        <v>39645</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-2244</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.0536</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1819</v>
+      </c>
+      <c r="I30" t="n">
+        <v>36776</v>
+      </c>
+      <c r="J30" t="n">
+        <v>39780</v>
+      </c>
+      <c r="K30" t="n">
+        <v>40556</v>
+      </c>
+      <c r="L30" t="n">
+        <v>41332</v>
+      </c>
+      <c r="M30" t="n">
+        <v>43222</v>
+      </c>
+      <c r="N30" t="n">
+        <v>45112</v>
+      </c>
+      <c r="O30" t="n">
+        <v>44774</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>42331</v>
+      </c>
+      <c r="C31" t="n">
+        <v>43951</v>
+      </c>
+      <c r="D31" t="n">
+        <v>39866</v>
+      </c>
+      <c r="E31" t="n">
+        <v>41859</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2214</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.0558</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4085</v>
+      </c>
+      <c r="I31" t="n">
+        <v>37628</v>
+      </c>
+      <c r="J31" t="n">
+        <v>37470.25</v>
+      </c>
+      <c r="K31" t="n">
+        <v>38735.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>40000.75</v>
+      </c>
+      <c r="M31" t="n">
+        <v>40554.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>41108.25</v>
+      </c>
+      <c r="O31" t="n">
+        <v>43085</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>43186</v>
+      </c>
+      <c r="C32" t="n">
+        <v>43873</v>
+      </c>
+      <c r="D32" t="n">
+        <v>42086</v>
+      </c>
+      <c r="E32" t="n">
+        <v>42650</v>
+      </c>
+      <c r="F32" t="n">
+        <v>791</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1787</v>
+      </c>
+      <c r="I32" t="n">
+        <v>35781</v>
+      </c>
+      <c r="J32" t="n">
+        <v>37749.25</v>
+      </c>
+      <c r="K32" t="n">
+        <v>39816.5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>41883.75</v>
+      </c>
+      <c r="M32" t="n">
+        <v>43901.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>45919.25</v>
+      </c>
+      <c r="O32" t="n">
+        <v>48036</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>42750</v>
+      </c>
+      <c r="C33" t="n">
+        <v>43790</v>
+      </c>
+      <c r="D33" t="n">
+        <v>42104</v>
+      </c>
+      <c r="E33" t="n">
+        <v>43152</v>
+      </c>
+      <c r="F33" t="n">
+        <v>502</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1686</v>
+      </c>
+      <c r="I33" t="n">
+        <v>40299</v>
+      </c>
+      <c r="J33" t="n">
+        <v>40698.25</v>
+      </c>
+      <c r="K33" t="n">
+        <v>41756.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>42814.75</v>
+      </c>
+      <c r="M33" t="n">
+        <v>43543.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>44272.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>45660</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>44653</v>
+      </c>
+      <c r="C34" t="n">
+        <v>44923</v>
+      </c>
+      <c r="D34" t="n">
+        <v>43233</v>
+      </c>
+      <c r="E34" t="n">
+        <v>44539</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1387</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.0321</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1690</v>
+      </c>
+      <c r="I34" t="n">
+        <v>40418</v>
+      </c>
+      <c r="J34" t="n">
+        <v>41568.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>42309</v>
+      </c>
+      <c r="L34" t="n">
+        <v>43049.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>43995</v>
+      </c>
+      <c r="N34" t="n">
+        <v>44940.5</v>
+      </c>
+      <c r="O34" t="n">
+        <v>45476</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>44177</v>
+      </c>
+      <c r="C35" t="n">
+        <v>44644</v>
+      </c>
+      <c r="D35" t="n">
+        <v>43843</v>
+      </c>
+      <c r="E35" t="n">
+        <v>44278</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-261</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="H35" t="n">
+        <v>801</v>
+      </c>
+      <c r="I35" t="n">
+        <v>41543</v>
+      </c>
+      <c r="J35" t="n">
+        <v>43079.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>43694</v>
+      </c>
+      <c r="L35" t="n">
+        <v>44308.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>45384</v>
+      </c>
+      <c r="N35" t="n">
+        <v>46459.5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>46613</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>44588</v>
+      </c>
+      <c r="C36" t="n">
+        <v>44873</v>
+      </c>
+      <c r="D36" t="n">
+        <v>43800</v>
+      </c>
+      <c r="E36" t="n">
+        <v>44543</v>
+      </c>
+      <c r="F36" t="n">
+        <v>265</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1073</v>
+      </c>
+      <c r="I36" t="n">
+        <v>43042</v>
+      </c>
+      <c r="J36" t="n">
+        <v>43494.25</v>
+      </c>
+      <c r="K36" t="n">
+        <v>43877.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>44260.75</v>
+      </c>
+      <c r="M36" t="n">
+        <v>44678.5</v>
+      </c>
+      <c r="N36" t="n">
+        <v>45096.25</v>
+      </c>
+      <c r="O36" t="n">
+        <v>45445</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>44985</v>
+      </c>
+      <c r="C37" t="n">
+        <v>45246</v>
+      </c>
+      <c r="D37" t="n">
+        <v>44362</v>
+      </c>
+      <c r="E37" t="n">
+        <v>45033</v>
+      </c>
+      <c r="F37" t="n">
+        <v>490</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="H37" t="n">
+        <v>884</v>
+      </c>
+      <c r="I37" t="n">
+        <v>42727</v>
+      </c>
+      <c r="J37" t="n">
+        <v>43573.25</v>
+      </c>
+      <c r="K37" t="n">
+        <v>44006.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>44439.75</v>
+      </c>
+      <c r="M37" t="n">
+        <v>45079.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>45719.25</v>
+      </c>
+      <c r="O37" t="n">
+        <v>45946</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>44761</v>
+      </c>
+      <c r="C38" t="n">
+        <v>45200</v>
+      </c>
+      <c r="D38" t="n">
+        <v>44570</v>
+      </c>
+      <c r="E38" t="n">
+        <v>44719</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-314</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="H38" t="n">
+        <v>630</v>
+      </c>
+      <c r="I38" t="n">
+        <v>43478</v>
+      </c>
+      <c r="J38" t="n">
+        <v>44263.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>44591</v>
+      </c>
+      <c r="L38" t="n">
+        <v>44918.5</v>
+      </c>
+      <c r="M38" t="n">
+        <v>45475</v>
+      </c>
+      <c r="N38" t="n">
+        <v>46031.5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>46130</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C39" t="n">
+        <v>45561</v>
+      </c>
+      <c r="D39" t="n">
+        <v>44830</v>
+      </c>
+      <c r="E39" t="n">
+        <v>45279</v>
+      </c>
+      <c r="F39" t="n">
+        <v>560</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="H39" t="n">
+        <v>731</v>
+      </c>
+      <c r="I39" t="n">
+        <v>43940</v>
+      </c>
+      <c r="J39" t="n">
+        <v>44006</v>
+      </c>
+      <c r="K39" t="n">
+        <v>44404</v>
+      </c>
+      <c r="L39" t="n">
+        <v>44802</v>
+      </c>
+      <c r="M39" t="n">
+        <v>45034</v>
+      </c>
+      <c r="N39" t="n">
+        <v>45266</v>
+      </c>
+      <c r="O39" t="n">
+        <v>45830</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>46120</v>
+      </c>
+      <c r="C40" t="n">
+        <v>46312</v>
+      </c>
+      <c r="D40" t="n">
+        <v>45590</v>
+      </c>
+      <c r="E40" t="n">
+        <v>46117</v>
+      </c>
+      <c r="F40" t="n">
+        <v>838</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="H40" t="n">
+        <v>722</v>
+      </c>
+      <c r="I40" t="n">
+        <v>44099</v>
+      </c>
+      <c r="J40" t="n">
+        <v>44589.75</v>
+      </c>
+      <c r="K40" t="n">
+        <v>44913.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>45237.25</v>
+      </c>
+      <c r="M40" t="n">
+        <v>45644.5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>46051.75</v>
+      </c>
+      <c r="O40" t="n">
+        <v>46292</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>46466</v>
+      </c>
+      <c r="C41" t="n">
+        <v>46574</v>
+      </c>
+      <c r="D41" t="n">
+        <v>45676</v>
+      </c>
+      <c r="E41" t="n">
+        <v>46389</v>
+      </c>
+      <c r="F41" t="n">
+        <v>272</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="H41" t="n">
+        <v>898</v>
+      </c>
+      <c r="I41" t="n">
+        <v>44868</v>
+      </c>
+      <c r="J41" t="n">
+        <v>45478</v>
+      </c>
+      <c r="K41" t="n">
+        <v>45756</v>
+      </c>
+      <c r="L41" t="n">
+        <v>46034</v>
+      </c>
+      <c r="M41" t="n">
+        <v>46478</v>
+      </c>
+      <c r="N41" t="n">
+        <v>46922</v>
+      </c>
+      <c r="O41" t="n">
+        <v>47034</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W41" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>45850</v>
+      </c>
+      <c r="C42" t="n">
+        <v>46140</v>
+      </c>
+      <c r="D42" t="n">
+        <v>45551</v>
+      </c>
+      <c r="E42" t="n">
+        <v>45727</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-662</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="H42" t="n">
+        <v>589</v>
+      </c>
+      <c r="I42" t="n">
+        <v>44778</v>
+      </c>
+      <c r="J42" t="n">
+        <v>45623</v>
+      </c>
+      <c r="K42" t="n">
+        <v>45940</v>
+      </c>
+      <c r="L42" t="n">
+        <v>46257</v>
+      </c>
+      <c r="M42" t="n">
+        <v>46838</v>
+      </c>
+      <c r="N42" t="n">
+        <v>47419</v>
+      </c>
+      <c r="O42" t="n">
+        <v>47472</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>45967</v>
+      </c>
+      <c r="C43" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D43" t="n">
+        <v>45070</v>
+      </c>
+      <c r="E43" t="n">
+        <v>45811</v>
+      </c>
+      <c r="F43" t="n">
+        <v>84</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1227</v>
+      </c>
+      <c r="I43" t="n">
+        <v>44962</v>
+      </c>
+      <c r="J43" t="n">
+        <v>45078.75</v>
+      </c>
+      <c r="K43" t="n">
+        <v>45432.5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>45786.25</v>
+      </c>
+      <c r="M43" t="n">
+        <v>46021.5</v>
+      </c>
+      <c r="N43" t="n">
+        <v>46256.75</v>
+      </c>
+      <c r="O43" t="n">
+        <v>46729</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>44411</v>
+      </c>
+      <c r="C44" t="n">
+        <v>45208</v>
+      </c>
+      <c r="D44" t="n">
+        <v>44208</v>
+      </c>
+      <c r="E44" t="n">
+        <v>44527</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-1284</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I44" t="n">
+        <v>43843</v>
+      </c>
+      <c r="J44" t="n">
+        <v>44647.75</v>
+      </c>
+      <c r="K44" t="n">
+        <v>45197.5</v>
+      </c>
+      <c r="L44" t="n">
+        <v>45747.25</v>
+      </c>
+      <c r="M44" t="n">
+        <v>46424.5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>47101.75</v>
+      </c>
+      <c r="O44" t="n">
+        <v>47524</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44950</v>
+      </c>
+      <c r="C45" t="n">
+        <v>45196</v>
+      </c>
+      <c r="D45" t="n">
+        <v>44448</v>
+      </c>
+      <c r="E45" t="n">
+        <v>44802</v>
+      </c>
+      <c r="F45" t="n">
+        <v>275</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="H45" t="n">
+        <v>748</v>
+      </c>
+      <c r="I45" t="n">
+        <v>43208</v>
+      </c>
+      <c r="J45" t="n">
+        <v>43436.5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>44027</v>
+      </c>
+      <c r="L45" t="n">
+        <v>44617.5</v>
+      </c>
+      <c r="M45" t="n">
+        <v>45027</v>
+      </c>
+      <c r="N45" t="n">
+        <v>45436.5</v>
+      </c>
+      <c r="O45" t="n">
+        <v>46208</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>44887</v>
+      </c>
+      <c r="C46" t="n">
+        <v>45294</v>
+      </c>
+      <c r="D46" t="n">
+        <v>44261</v>
+      </c>
+      <c r="E46" t="n">
+        <v>44804</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1033</v>
+      </c>
+      <c r="I46" t="n">
+        <v>43700</v>
+      </c>
+      <c r="J46" t="n">
+        <v>44044</v>
+      </c>
+      <c r="K46" t="n">
+        <v>44428</v>
+      </c>
+      <c r="L46" t="n">
+        <v>44812</v>
+      </c>
+      <c r="M46" t="n">
+        <v>45176</v>
+      </c>
+      <c r="N46" t="n">
+        <v>45540</v>
+      </c>
+      <c r="O46" t="n">
+        <v>45944</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>45032</v>
+      </c>
+      <c r="C47" t="n">
+        <v>45474</v>
+      </c>
+      <c r="D47" t="n">
+        <v>44609</v>
+      </c>
+      <c r="E47" t="n">
+        <v>45074</v>
+      </c>
+      <c r="F47" t="n">
+        <v>270</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H47" t="n">
+        <v>865</v>
+      </c>
+      <c r="I47" t="n">
+        <v>43228</v>
+      </c>
+      <c r="J47" t="n">
+        <v>43784.25</v>
+      </c>
+      <c r="K47" t="n">
+        <v>44287.5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>44790.75</v>
+      </c>
+      <c r="M47" t="n">
+        <v>45320.5</v>
+      </c>
+      <c r="N47" t="n">
+        <v>45850.25</v>
+      </c>
+      <c r="O47" t="n">
+        <v>46327</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>44488</v>
+      </c>
+      <c r="C48" t="n">
+        <v>45095</v>
+      </c>
+      <c r="D48" t="n">
+        <v>44146</v>
+      </c>
+      <c r="E48" t="n">
+        <v>44532</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-542</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="H48" t="n">
+        <v>949</v>
+      </c>
+      <c r="I48" t="n">
+        <v>43744</v>
+      </c>
+      <c r="J48" t="n">
+        <v>44225.25</v>
+      </c>
+      <c r="K48" t="n">
+        <v>44641.5</v>
+      </c>
+      <c r="L48" t="n">
+        <v>45057.75</v>
+      </c>
+      <c r="M48" t="n">
+        <v>45506.5</v>
+      </c>
+      <c r="N48" t="n">
+        <v>45955.25</v>
+      </c>
+      <c r="O48" t="n">
+        <v>46339</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>45285</v>
+      </c>
+      <c r="C49" t="n">
+        <v>46027</v>
+      </c>
+      <c r="D49" t="n">
+        <v>44865</v>
+      </c>
+      <c r="E49" t="n">
+        <v>45437</v>
+      </c>
+      <c r="F49" t="n">
+        <v>905</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1162</v>
+      </c>
+      <c r="I49" t="n">
+        <v>43197</v>
+      </c>
+      <c r="J49" t="n">
+        <v>43538.75</v>
+      </c>
+      <c r="K49" t="n">
+        <v>44057.5</v>
+      </c>
+      <c r="L49" t="n">
+        <v>44576.25</v>
+      </c>
+      <c r="M49" t="n">
+        <v>45006.5</v>
+      </c>
+      <c r="N49" t="n">
+        <v>45436.75</v>
+      </c>
+      <c r="O49" t="n">
+        <v>46044</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C50" t="n">
+        <v>46517</v>
+      </c>
+      <c r="D50" t="n">
+        <v>45766</v>
+      </c>
+      <c r="E50" t="n">
+        <v>45993</v>
+      </c>
+      <c r="F50" t="n">
+        <v>556</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="H50" t="n">
+        <v>751</v>
+      </c>
+      <c r="I50" t="n">
+        <v>43703</v>
+      </c>
+      <c r="J50" t="n">
+        <v>44270.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>44856</v>
+      </c>
+      <c r="L50" t="n">
+        <v>45441.5</v>
+      </c>
+      <c r="M50" t="n">
+        <v>46018</v>
+      </c>
+      <c r="N50" t="n">
+        <v>46594.5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>47189</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>46366</v>
+      </c>
+      <c r="C51" t="n">
+        <v>46580</v>
+      </c>
+      <c r="D51" t="n">
+        <v>46036</v>
+      </c>
+      <c r="E51" t="n">
+        <v>46388</v>
+      </c>
+      <c r="F51" t="n">
+        <v>395</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="H51" t="n">
+        <v>544</v>
+      </c>
+      <c r="I51" t="n">
+        <v>45015</v>
+      </c>
+      <c r="J51" t="n">
+        <v>45167.75</v>
+      </c>
+      <c r="K51" t="n">
+        <v>45617.5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>46067.25</v>
+      </c>
+      <c r="M51" t="n">
+        <v>46368.5</v>
+      </c>
+      <c r="N51" t="n">
+        <v>46669.75</v>
+      </c>
+      <c r="O51" t="n">
+        <v>47268</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>45800</v>
+      </c>
+      <c r="C52" t="n">
+        <v>46613</v>
+      </c>
+      <c r="D52" t="n">
+        <v>45415</v>
+      </c>
+      <c r="E52" t="n">
+        <v>45900</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-488</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1198</v>
+      </c>
+      <c r="I52" t="n">
+        <v>45492</v>
+      </c>
+      <c r="J52" t="n">
+        <v>45884</v>
+      </c>
+      <c r="K52" t="n">
+        <v>46116</v>
+      </c>
+      <c r="L52" t="n">
+        <v>46348</v>
+      </c>
+      <c r="M52" t="n">
+        <v>46660</v>
+      </c>
+      <c r="N52" t="n">
+        <v>46972</v>
+      </c>
+      <c r="O52" t="n">
+        <v>47124</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W52" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>46000</v>
+      </c>
+      <c r="C53" t="n">
+        <v>47220</v>
+      </c>
+      <c r="D53" t="n">
+        <v>45788</v>
+      </c>
+      <c r="E53" t="n">
+        <v>45978</v>
+      </c>
+      <c r="F53" t="n">
+        <v>78</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1432</v>
+      </c>
+      <c r="I53" t="n">
+        <v>44217</v>
+      </c>
+      <c r="J53" t="n">
+        <v>44645</v>
+      </c>
+      <c r="K53" t="n">
+        <v>45301</v>
+      </c>
+      <c r="L53" t="n">
+        <v>45957</v>
+      </c>
+      <c r="M53" t="n">
+        <v>46499</v>
+      </c>
+      <c r="N53" t="n">
+        <v>47041</v>
+      </c>
+      <c r="O53" t="n">
+        <v>47811</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>46701</v>
+      </c>
+      <c r="C54" t="n">
+        <v>47343</v>
+      </c>
+      <c r="D54" t="n">
+        <v>46131</v>
+      </c>
+      <c r="E54" t="n">
+        <v>46679</v>
+      </c>
+      <c r="F54" t="n">
+        <v>701</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1212</v>
+      </c>
+      <c r="I54" t="n">
+        <v>44356</v>
+      </c>
+      <c r="J54" t="n">
+        <v>44283</v>
+      </c>
+      <c r="K54" t="n">
+        <v>45262</v>
+      </c>
+      <c r="L54" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M54" t="n">
+        <v>46694</v>
+      </c>
+      <c r="N54" t="n">
+        <v>47147</v>
+      </c>
+      <c r="O54" t="n">
+        <v>48652</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C55" t="n">
+        <v>46472</v>
+      </c>
+      <c r="D55" t="n">
+        <v>45686</v>
+      </c>
+      <c r="E55" t="n">
+        <v>46336</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-343</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="H55" t="n">
+        <v>786</v>
+      </c>
+      <c r="I55" t="n">
+        <v>44919</v>
+      </c>
+      <c r="J55" t="n">
+        <v>45438</v>
+      </c>
+      <c r="K55" t="n">
+        <v>46073</v>
+      </c>
+      <c r="L55" t="n">
+        <v>46708</v>
+      </c>
+      <c r="M55" t="n">
+        <v>47285</v>
+      </c>
+      <c r="N55" t="n">
+        <v>47862</v>
+      </c>
+      <c r="O55" t="n">
+        <v>48555</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>46406</v>
+      </c>
+      <c r="C56" t="n">
+        <v>46756</v>
+      </c>
+      <c r="D56" t="n">
+        <v>45726</v>
+      </c>
+      <c r="E56" t="n">
+        <v>46487</v>
+      </c>
+      <c r="F56" t="n">
+        <v>151</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1030</v>
+      </c>
+      <c r="I56" t="n">
+        <v>44900</v>
+      </c>
+      <c r="J56" t="n">
+        <v>45678.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>45943</v>
+      </c>
+      <c r="L56" t="n">
+        <v>46207.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>46729</v>
+      </c>
+      <c r="N56" t="n">
+        <v>47250.5</v>
+      </c>
+      <c r="O56" t="n">
+        <v>47258</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>47280</v>
+      </c>
+      <c r="C57" t="n">
+        <v>47572</v>
+      </c>
+      <c r="D57" t="n">
+        <v>46560</v>
+      </c>
+      <c r="E57" t="n">
+        <v>47182</v>
+      </c>
+      <c r="F57" t="n">
+        <v>695</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1012</v>
+      </c>
+      <c r="I57" t="n">
+        <v>44696</v>
+      </c>
+      <c r="J57" t="n">
+        <v>45580</v>
+      </c>
+      <c r="K57" t="n">
+        <v>45972</v>
+      </c>
+      <c r="L57" t="n">
+        <v>46364</v>
+      </c>
+      <c r="M57" t="n">
+        <v>47002</v>
+      </c>
+      <c r="N57" t="n">
+        <v>47640</v>
+      </c>
+      <c r="O57" t="n">
+        <v>47786</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>47480</v>
+      </c>
+      <c r="C58" t="n">
+        <v>47593</v>
+      </c>
+      <c r="D58" t="n">
+        <v>46934</v>
+      </c>
+      <c r="E58" t="n">
+        <v>47329</v>
+      </c>
+      <c r="F58" t="n">
+        <v>147</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="H58" t="n">
+        <v>659</v>
+      </c>
+      <c r="I58" t="n">
+        <v>45548</v>
+      </c>
+      <c r="J58" t="n">
+        <v>46228</v>
+      </c>
+      <c r="K58" t="n">
+        <v>46676</v>
+      </c>
+      <c r="L58" t="n">
+        <v>47124</v>
+      </c>
+      <c r="M58" t="n">
+        <v>47688</v>
+      </c>
+      <c r="N58" t="n">
+        <v>48252</v>
+      </c>
+      <c r="O58" t="n">
+        <v>48584</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>47076</v>
+      </c>
+      <c r="C59" t="n">
+        <v>47592</v>
+      </c>
+      <c r="D59" t="n">
+        <v>46561</v>
+      </c>
+      <c r="E59" t="n">
+        <v>47055</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-274</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1031</v>
+      </c>
+      <c r="I59" t="n">
+        <v>46275</v>
+      </c>
+      <c r="J59" t="n">
+        <v>46702.75</v>
+      </c>
+      <c r="K59" t="n">
+        <v>46999.5</v>
+      </c>
+      <c r="L59" t="n">
+        <v>47296.25</v>
+      </c>
+      <c r="M59" t="n">
+        <v>47658.5</v>
+      </c>
+      <c r="N59" t="n">
+        <v>48020.75</v>
+      </c>
+      <c r="O59" t="n">
+        <v>48252</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W59" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B60" t="n">
         <v>46940</v>
       </c>
-      <c r="C9" t="n">
-        <v>46950</v>
-      </c>
-      <c r="D9" t="n">
-        <v>46015</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="C60" t="n">
+        <v>47295</v>
+      </c>
+      <c r="D60" t="n">
+        <v>46506</v>
+      </c>
+      <c r="E60" t="n">
+        <v>46984</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-71</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="H60" t="n">
+        <v>789</v>
+      </c>
+      <c r="I60" t="n">
+        <v>45530</v>
+      </c>
+      <c r="J60" t="n">
+        <v>46013.25</v>
+      </c>
+      <c r="K60" t="n">
+        <v>46539.5</v>
+      </c>
+      <c r="L60" t="n">
+        <v>47065.75</v>
+      </c>
+      <c r="M60" t="n">
+        <v>47570.5</v>
+      </c>
+      <c r="N60" t="n">
+        <v>48075.25</v>
+      </c>
+      <c r="O60" t="n">
+        <v>48623</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W60" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>45820</v>
+      </c>
+      <c r="C61" t="n">
+        <v>46896</v>
+      </c>
+      <c r="D61" t="n">
+        <v>45780</v>
+      </c>
+      <c r="E61" t="n">
         <v>46072</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F61" t="n">
         <v>-912</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G61" s="5" t="n">
         <v>-0.0194</v>
       </c>
-      <c r="H9" t="n">
-        <v>935</v>
-      </c>
-      <c r="I9" t="n">
-        <v>45902</v>
-      </c>
-      <c r="J9" t="n">
-        <v>46046.25</v>
-      </c>
-      <c r="K9" t="n">
-        <v>46561.5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>47076.75</v>
-      </c>
-      <c r="M9" t="n">
-        <v>47406.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>47736.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>48437</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="H61" t="n">
+        <v>1116</v>
+      </c>
+      <c r="I61" t="n">
+        <v>45717</v>
+      </c>
+      <c r="J61" t="n">
+        <v>46236.75</v>
+      </c>
+      <c r="K61" t="n">
+        <v>46589.5</v>
+      </c>
+      <c r="L61" t="n">
+        <v>46942.25</v>
+      </c>
+      <c r="M61" t="n">
+        <v>47378.5</v>
+      </c>
+      <c r="N61" t="n">
+        <v>47814.75</v>
+      </c>
+      <c r="O61" t="n">
+        <v>48084</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="11" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="9" t="inlineStr"/>
-      <c r="W9" s="10" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>45589</v>
+      </c>
+      <c r="C62" t="n">
+        <v>46663</v>
+      </c>
+      <c r="D62" t="n">
+        <v>45302</v>
+      </c>
+      <c r="E62" t="n">
+        <v>46588</v>
+      </c>
+      <c r="F62" t="n">
+        <v>516</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1361</v>
+      </c>
+      <c r="I62" t="n">
+        <v>44664</v>
+      </c>
+      <c r="J62" t="n">
+        <v>44823</v>
+      </c>
+      <c r="K62" t="n">
+        <v>45514</v>
+      </c>
+      <c r="L62" t="n">
+        <v>46205</v>
+      </c>
+      <c r="M62" t="n">
+        <v>46630</v>
+      </c>
+      <c r="N62" t="n">
+        <v>47055</v>
+      </c>
+      <c r="O62" t="n">
+        <v>48012</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>45777</v>
+      </c>
+      <c r="C63" t="n">
+        <v>45964</v>
+      </c>
+      <c r="D63" t="n">
+        <v>45361</v>
+      </c>
+      <c r="E63" t="n">
+        <v>45556</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-1032</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="H63" t="n">
+        <v>603</v>
+      </c>
+      <c r="I63" t="n">
+        <v>43941</v>
+      </c>
+      <c r="J63" t="n">
+        <v>45529.75</v>
+      </c>
+      <c r="K63" t="n">
+        <v>45907.5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>46285.25</v>
+      </c>
+      <c r="M63" t="n">
+        <v>47268.5</v>
+      </c>
+      <c r="N63" t="n">
+        <v>48251.75</v>
+      </c>
+      <c r="O63" t="n">
+        <v>48024</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>45533</v>
+      </c>
+      <c r="C64" t="n">
+        <v>45736</v>
+      </c>
+      <c r="D64" t="n">
+        <v>45330</v>
+      </c>
+      <c r="E64" t="n">
+        <v>45529</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-27</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="H64" t="n">
+        <v>406</v>
+      </c>
+      <c r="I64" t="n">
+        <v>44758</v>
+      </c>
+      <c r="J64" t="n">
+        <v>44899.75</v>
+      </c>
+      <c r="K64" t="n">
+        <v>45254.5</v>
+      </c>
+      <c r="L64" t="n">
+        <v>45609.25</v>
+      </c>
+      <c r="M64" t="n">
+        <v>45857.5</v>
+      </c>
+      <c r="N64" t="n">
+        <v>46105.75</v>
+      </c>
+      <c r="O64" t="n">
+        <v>46567</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I10" s="14" t="n">
-        <v>45080</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>44931.75</v>
-      </c>
-      <c r="K10" s="14" t="n">
-        <v>45604.5</v>
-      </c>
-      <c r="L10" s="14" t="n">
-        <v>46277.25</v>
-      </c>
-      <c r="M10" s="14" t="n">
-        <v>46539.5</v>
-      </c>
-      <c r="N10" s="14" t="n">
-        <v>46801.75</v>
-      </c>
-      <c r="O10" s="14" t="n">
-        <v>47885</v>
+      <c r="I65" s="13" t="n">
+        <v>44924</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>45121</v>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>45326</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>45531</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>45732</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>45933</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>46142</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>45533</v>
+        <v>45534</v>
       </c>
       <c r="C64" t="n">
-        <v>45736</v>
+        <v>46093</v>
       </c>
       <c r="D64" t="n">
         <v>45330</v>
@@ -5847,7 +5847,7 @@
         <v>-0.0005999999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>406</v>
+        <v>763</v>
       </c>
       <c r="I64" t="n">
         <v>44758</v>
@@ -5884,8 +5884,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T64" s="8" t="n">
-        <v/>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5898,7 +5900,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -5907,25 +5913,25 @@
         </is>
       </c>
       <c r="I65" s="13" t="n">
-        <v>44924</v>
+        <v>44567</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>45121</v>
+        <v>44674.75</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>45326</v>
+        <v>45147.5</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>45531</v>
+        <v>45620.25</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>45732</v>
+        <v>45910.5</v>
       </c>
       <c r="N65" s="13" t="n">
-        <v>45933</v>
+        <v>46200.75</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>46142</v>
+        <v>46856</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5907,31 +5907,113 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>46153</v>
+      </c>
+      <c r="C65" t="n">
+        <v>46626</v>
+      </c>
+      <c r="D65" t="n">
+        <v>46056</v>
+      </c>
+      <c r="E65" t="n">
+        <v>46382</v>
+      </c>
+      <c r="F65" t="n">
+        <v>853</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="H65" t="n">
+        <v>570</v>
+      </c>
+      <c r="I65" t="n">
+        <v>44567</v>
+      </c>
+      <c r="J65" t="n">
+        <v>44674.75</v>
+      </c>
+      <c r="K65" t="n">
+        <v>45147.5</v>
+      </c>
+      <c r="L65" t="n">
+        <v>45620.25</v>
+      </c>
+      <c r="M65" t="n">
+        <v>45910.5</v>
+      </c>
+      <c r="N65" t="n">
+        <v>46200.75</v>
+      </c>
+      <c r="O65" t="n">
+        <v>46856</v>
+      </c>
+      <c r="P65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W65" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="13" t="n">
-        <v>44567</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>44674.75</v>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>45147.5</v>
-      </c>
-      <c r="L65" s="13" t="n">
-        <v>45620.25</v>
-      </c>
-      <c r="M65" s="13" t="n">
-        <v>45910.5</v>
-      </c>
-      <c r="N65" s="13" t="n">
-        <v>46200.75</v>
-      </c>
-      <c r="O65" s="13" t="n">
-        <v>46856</v>
+      <c r="I66" s="13" t="n">
+        <v>45486</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>45832.5</v>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>46097</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>46361.5</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>46667</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>46972.5</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>47196</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -5749,19 +5749,19 @@
         <v>45964</v>
       </c>
       <c r="D63" t="n">
-        <v>45361</v>
+        <v>45330</v>
       </c>
       <c r="E63" t="n">
-        <v>45556</v>
+        <v>45529</v>
       </c>
       <c r="F63" t="n">
-        <v>-1032</v>
+        <v>-1059</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0222</v>
+        <v>-0.0227</v>
       </c>
       <c r="H63" t="n">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="I63" t="n">
         <v>43941</v>
@@ -5829,46 +5829,46 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>45534</v>
+        <v>45687</v>
       </c>
       <c r="C64" t="n">
-        <v>46093</v>
+        <v>46626</v>
       </c>
       <c r="D64" t="n">
-        <v>45330</v>
+        <v>45678</v>
       </c>
       <c r="E64" t="n">
-        <v>45529</v>
+        <v>46382</v>
       </c>
       <c r="F64" t="n">
-        <v>-27</v>
+        <v>853</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0187</v>
       </c>
       <c r="H64" t="n">
-        <v>763</v>
+        <v>948</v>
       </c>
       <c r="I64" t="n">
-        <v>44758</v>
+        <v>44696</v>
       </c>
       <c r="J64" t="n">
-        <v>44899.75</v>
+        <v>44836</v>
       </c>
       <c r="K64" t="n">
-        <v>45254.5</v>
+        <v>45212</v>
       </c>
       <c r="L64" t="n">
-        <v>45609.25</v>
+        <v>45588</v>
       </c>
       <c r="M64" t="n">
-        <v>45857.5</v>
+        <v>45846</v>
       </c>
       <c r="N64" t="n">
-        <v>46105.75</v>
+        <v>46104</v>
       </c>
       <c r="O64" t="n">
-        <v>46567</v>
+        <v>46598</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5879,9 +5879,9 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
@@ -5889,22 +5889,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V64" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W64" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5913,46 +5913,46 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>46153</v>
+        <v>46495</v>
       </c>
       <c r="C65" t="n">
-        <v>46626</v>
+        <v>47205</v>
       </c>
       <c r="D65" t="n">
-        <v>46056</v>
+        <v>46376</v>
       </c>
       <c r="E65" t="n">
-        <v>46382</v>
+        <v>47160</v>
       </c>
       <c r="F65" t="n">
-        <v>853</v>
+        <v>778</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0187</v>
+        <v>0.0168</v>
       </c>
       <c r="H65" t="n">
-        <v>570</v>
+        <v>829</v>
       </c>
       <c r="I65" t="n">
-        <v>44567</v>
+        <v>44730</v>
       </c>
       <c r="J65" t="n">
-        <v>44674.75</v>
+        <v>45549</v>
       </c>
       <c r="K65" t="n">
-        <v>45147.5</v>
+        <v>45908</v>
       </c>
       <c r="L65" t="n">
-        <v>45620.25</v>
+        <v>46267</v>
       </c>
       <c r="M65" t="n">
-        <v>45910.5</v>
+        <v>46856</v>
       </c>
       <c r="N65" t="n">
-        <v>46200.75</v>
+        <v>47445</v>
       </c>
       <c r="O65" t="n">
-        <v>46856</v>
+        <v>47574</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5995,25 +5995,25 @@
         </is>
       </c>
       <c r="I66" s="13" t="n">
-        <v>45486</v>
+        <v>45547</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>45832.5</v>
+        <v>46515.75</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>46097</v>
+        <v>46745.5</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>46361.5</v>
+        <v>46975.25</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>46667</v>
+        <v>47574.5</v>
       </c>
       <c r="N66" s="13" t="n">
-        <v>46972.5</v>
+        <v>48173.75</v>
       </c>
       <c r="O66" s="13" t="n">
-        <v>47196</v>
+        <v>48034</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5989,32 +5982,84 @@
       <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I66" s="13" t="n">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>46594</v>
+      </c>
+      <c r="C66" t="n">
+        <v>47205</v>
+      </c>
+      <c r="D66" t="n">
+        <v>46538</v>
+      </c>
+      <c r="E66" t="n">
+        <v>47160</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>667</v>
+      </c>
+      <c r="I66" t="n">
         <v>45547</v>
       </c>
-      <c r="J66" s="13" t="n">
+      <c r="J66" t="n">
         <v>46515.75</v>
       </c>
-      <c r="K66" s="13" t="n">
+      <c r="K66" t="n">
         <v>46745.5</v>
       </c>
-      <c r="L66" s="13" t="n">
+      <c r="L66" t="n">
         <v>46975.25</v>
       </c>
-      <c r="M66" s="13" t="n">
+      <c r="M66" t="n">
         <v>47574.5</v>
       </c>
-      <c r="N66" s="13" t="n">
+      <c r="N66" t="n">
         <v>48173.75</v>
       </c>
-      <c r="O66" s="13" t="n">
+      <c r="O66" t="n">
         <v>48034</v>
       </c>
+      <c r="P66" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q66" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U66" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V66" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W66" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -5988,25 +5988,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>46594</v>
+        <v>47080</v>
       </c>
       <c r="C66" t="n">
-        <v>47205</v>
+        <v>47464</v>
       </c>
       <c r="D66" t="n">
-        <v>46538</v>
+        <v>46897</v>
       </c>
       <c r="E66" t="n">
-        <v>47160</v>
+        <v>47418</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="H66" t="n">
-        <v>667</v>
+        <v>567</v>
       </c>
       <c r="I66" t="n">
         <v>45547</v>
@@ -6035,18 +6035,18 @@
       <c r="Q66" s="6" t="n">
         <v/>
       </c>
-      <c r="R66" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R66" s="6" t="n">
+        <v/>
       </c>
       <c r="S66" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T66" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U66" s="8" t="n">
         <v/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X66"/>
+  <dimension ref="A1:X67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6061,6 +6061,90 @@
       </c>
       <c r="X66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>47607</v>
+      </c>
+      <c r="C67" t="n">
+        <v>48805</v>
+      </c>
+      <c r="D67" t="n">
+        <v>47496</v>
+      </c>
+      <c r="E67" t="n">
+        <v>48781</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1363</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1309</v>
+      </c>
+      <c r="I67" t="n">
+        <v>46330</v>
+      </c>
+      <c r="J67" t="n">
+        <v>46969.75</v>
+      </c>
+      <c r="K67" t="n">
+        <v>47134.5</v>
+      </c>
+      <c r="L67" t="n">
+        <v>47299.25</v>
+      </c>
+      <c r="M67" t="n">
+        <v>47701.5</v>
+      </c>
+      <c r="N67" t="n">
+        <v>48103.75</v>
+      </c>
+      <c r="O67" t="n">
+        <v>48031</v>
+      </c>
+      <c r="P67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U67" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W67" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X67"/>
+  <dimension ref="A1:X68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6145,6 +6145,90 @@
       </c>
       <c r="X67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>48888</v>
+      </c>
+      <c r="C68" t="n">
+        <v>48946</v>
+      </c>
+      <c r="D68" t="n">
+        <v>48034</v>
+      </c>
+      <c r="E68" t="n">
+        <v>48243</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-538</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="H68" t="n">
+        <v>912</v>
+      </c>
+      <c r="I68" t="n">
+        <v>46187</v>
+      </c>
+      <c r="J68" t="n">
+        <v>47787.25</v>
+      </c>
+      <c r="K68" t="n">
+        <v>48126.5</v>
+      </c>
+      <c r="L68" t="n">
+        <v>48465.75</v>
+      </c>
+      <c r="M68" t="n">
+        <v>49435.5</v>
+      </c>
+      <c r="N68" t="n">
+        <v>50405.25</v>
+      </c>
+      <c r="O68" t="n">
+        <v>50114</v>
+      </c>
+      <c r="P68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S68" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U68" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V68" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W68" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -6158,19 +6158,19 @@
         <v>48946</v>
       </c>
       <c r="D68" t="n">
-        <v>48034</v>
+        <v>47876</v>
       </c>
       <c r="E68" t="n">
-        <v>48243</v>
+        <v>48497</v>
       </c>
       <c r="F68" t="n">
-        <v>-538</v>
+        <v>-284</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0058</v>
       </c>
       <c r="H68" t="n">
-        <v>912</v>
+        <v>1070</v>
       </c>
       <c r="I68" t="n">
         <v>46187</v>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S68" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T68" s="8" t="n">

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X68"/>
+  <dimension ref="A1:X69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6229,6 +6229,90 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>48186</v>
+      </c>
+      <c r="C69" t="n">
+        <v>48647</v>
+      </c>
+      <c r="D69" t="n">
+        <v>47876</v>
+      </c>
+      <c r="E69" t="n">
+        <v>48497</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>771</v>
+      </c>
+      <c r="I69" t="n">
+        <v>46806</v>
+      </c>
+      <c r="J69" t="n">
+        <v>47470</v>
+      </c>
+      <c r="K69" t="n">
+        <v>47962</v>
+      </c>
+      <c r="L69" t="n">
+        <v>48454</v>
+      </c>
+      <c r="M69" t="n">
+        <v>49032</v>
+      </c>
+      <c r="N69" t="n">
+        <v>49610</v>
+      </c>
+      <c r="O69" t="n">
+        <v>50016</v>
+      </c>
+      <c r="P69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S69" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U69" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V69" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W69" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -6236,25 +6236,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>48186</v>
+        <v>48529</v>
       </c>
       <c r="C69" t="n">
-        <v>48647</v>
+        <v>48623</v>
       </c>
       <c r="D69" t="n">
-        <v>47876</v>
+        <v>48223</v>
       </c>
       <c r="E69" t="n">
-        <v>48497</v>
+        <v>48336</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>-161</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0</v>
+        <v>-0.0033</v>
       </c>
       <c r="H69" t="n">
-        <v>771</v>
+        <v>400</v>
       </c>
       <c r="I69" t="n">
         <v>46806</v>
@@ -6283,14 +6283,12 @@
       <c r="Q69" s="6" t="n">
         <v/>
       </c>
-      <c r="R69" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S69" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S69" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T69" s="8" t="n">
@@ -6309,7 +6307,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -6242,19 +6242,19 @@
         <v>48623</v>
       </c>
       <c r="D69" t="n">
-        <v>48223</v>
+        <v>47783</v>
       </c>
       <c r="E69" t="n">
-        <v>48336</v>
+        <v>47909</v>
       </c>
       <c r="F69" t="n">
-        <v>-161</v>
+        <v>-588</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0121</v>
       </c>
       <c r="H69" t="n">
-        <v>400</v>
+        <v>840</v>
       </c>
       <c r="I69" t="n">
         <v>46806</v>
@@ -6283,12 +6283,14 @@
       <c r="Q69" s="6" t="n">
         <v/>
       </c>
-      <c r="R69" s="6" t="n">
-        <v/>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S69" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T69" s="8" t="n">
@@ -6307,7 +6309,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X69"/>
+  <dimension ref="A1:X70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6313,6 +6313,88 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>47850</v>
+      </c>
+      <c r="C70" t="n">
+        <v>48275</v>
+      </c>
+      <c r="D70" t="n">
+        <v>47797</v>
+      </c>
+      <c r="E70" t="n">
+        <v>48123</v>
+      </c>
+      <c r="F70" t="n">
+        <v>214</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="H70" t="n">
+        <v>478</v>
+      </c>
+      <c r="I70" t="n">
+        <v>46943</v>
+      </c>
+      <c r="J70" t="n">
+        <v>46922</v>
+      </c>
+      <c r="K70" t="n">
+        <v>47489</v>
+      </c>
+      <c r="L70" t="n">
+        <v>48056</v>
+      </c>
+      <c r="M70" t="n">
+        <v>48329</v>
+      </c>
+      <c r="N70" t="n">
+        <v>48602</v>
+      </c>
+      <c r="O70" t="n">
+        <v>49463</v>
+      </c>
+      <c r="P70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U70" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V70" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W70" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X70"/>
+  <dimension ref="A1:X71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6395,6 +6395,90 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>47915</v>
+      </c>
+      <c r="C71" t="n">
+        <v>48296</v>
+      </c>
+      <c r="D71" t="n">
+        <v>47769</v>
+      </c>
+      <c r="E71" t="n">
+        <v>47956</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-167</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="H71" t="n">
+        <v>527</v>
+      </c>
+      <c r="I71" t="n">
+        <v>47319</v>
+      </c>
+      <c r="J71" t="n">
+        <v>47688.5</v>
+      </c>
+      <c r="K71" t="n">
+        <v>47884</v>
+      </c>
+      <c r="L71" t="n">
+        <v>48079.5</v>
+      </c>
+      <c r="M71" t="n">
+        <v>48362</v>
+      </c>
+      <c r="N71" t="n">
+        <v>48644.5</v>
+      </c>
+      <c r="O71" t="n">
+        <v>48753</v>
+      </c>
+      <c r="P71" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q71" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S71" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U71" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V71" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W71" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X71"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6479,6 +6479,94 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>48098</v>
+      </c>
+      <c r="C72" t="n">
+        <v>48619</v>
+      </c>
+      <c r="D72" t="n">
+        <v>47630</v>
+      </c>
+      <c r="E72" t="n">
+        <v>48479</v>
+      </c>
+      <c r="F72" t="n">
+        <v>523</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="H72" t="n">
+        <v>989</v>
+      </c>
+      <c r="I72" t="n">
+        <v>47242</v>
+      </c>
+      <c r="J72" t="n">
+        <v>47390.75</v>
+      </c>
+      <c r="K72" t="n">
+        <v>47692.5</v>
+      </c>
+      <c r="L72" t="n">
+        <v>47994.25</v>
+      </c>
+      <c r="M72" t="n">
+        <v>48219.5</v>
+      </c>
+      <c r="N72" t="n">
+        <v>48444.75</v>
+      </c>
+      <c r="O72" t="n">
+        <v>48823</v>
+      </c>
+      <c r="P72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S72" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U72" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V72" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W72" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X72"/>
+  <dimension ref="A1:X73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6567,6 +6567,88 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>48467</v>
+      </c>
+      <c r="C73" t="n">
+        <v>48646</v>
+      </c>
+      <c r="D73" t="n">
+        <v>48158</v>
+      </c>
+      <c r="E73" t="n">
+        <v>48298</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-181</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="H73" t="n">
+        <v>488</v>
+      </c>
+      <c r="I73" t="n">
+        <v>46641</v>
+      </c>
+      <c r="J73" t="n">
+        <v>47667.25</v>
+      </c>
+      <c r="K73" t="n">
+        <v>47984.5</v>
+      </c>
+      <c r="L73" t="n">
+        <v>48301.75</v>
+      </c>
+      <c r="M73" t="n">
+        <v>48973.5</v>
+      </c>
+      <c r="N73" t="n">
+        <v>49645.25</v>
+      </c>
+      <c r="O73" t="n">
+        <v>49608</v>
+      </c>
+      <c r="P73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U73" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V73" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W73" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X73"/>
+  <dimension ref="A1:X74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6649,6 +6649,86 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>48398</v>
+      </c>
+      <c r="C74" t="n">
+        <v>48719</v>
+      </c>
+      <c r="D74" t="n">
+        <v>48168</v>
+      </c>
+      <c r="E74" t="n">
+        <v>48475</v>
+      </c>
+      <c r="F74" t="n">
+        <v>177</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="H74" t="n">
+        <v>551</v>
+      </c>
+      <c r="I74" t="n">
+        <v>47670</v>
+      </c>
+      <c r="J74" t="n">
+        <v>47758</v>
+      </c>
+      <c r="K74" t="n">
+        <v>48054</v>
+      </c>
+      <c r="L74" t="n">
+        <v>48350</v>
+      </c>
+      <c r="M74" t="n">
+        <v>48542</v>
+      </c>
+      <c r="N74" t="n">
+        <v>48734</v>
+      </c>
+      <c r="O74" t="n">
+        <v>49134</v>
+      </c>
+      <c r="P74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S74" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U74" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V74" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W74" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X74"/>
+  <dimension ref="A1:X75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6729,6 +6729,86 @@
       </c>
       <c r="X74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>48552</v>
+      </c>
+      <c r="C75" t="n">
+        <v>48802</v>
+      </c>
+      <c r="D75" t="n">
+        <v>48472</v>
+      </c>
+      <c r="E75" t="n">
+        <v>48671</v>
+      </c>
+      <c r="F75" t="n">
+        <v>196</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H75" t="n">
+        <v>330</v>
+      </c>
+      <c r="I75" t="n">
+        <v>47617</v>
+      </c>
+      <c r="J75" t="n">
+        <v>47939.75</v>
+      </c>
+      <c r="K75" t="n">
+        <v>48199.5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>48459.25</v>
+      </c>
+      <c r="M75" t="n">
+        <v>48750.5</v>
+      </c>
+      <c r="N75" t="n">
+        <v>49041.75</v>
+      </c>
+      <c r="O75" t="n">
+        <v>49270</v>
+      </c>
+      <c r="P75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S75" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U75" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V75" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W75" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X75"/>
+  <dimension ref="A1:X76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6809,6 +6809,90 @@
       </c>
       <c r="X75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>49470</v>
+      </c>
+      <c r="C76" t="n">
+        <v>50247</v>
+      </c>
+      <c r="D76" t="n">
+        <v>49461</v>
+      </c>
+      <c r="E76" t="n">
+        <v>50118</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1447</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="H76" t="n">
+        <v>786</v>
+      </c>
+      <c r="I76" t="n">
+        <v>48142</v>
+      </c>
+      <c r="J76" t="n">
+        <v>48358</v>
+      </c>
+      <c r="K76" t="n">
+        <v>48506</v>
+      </c>
+      <c r="L76" t="n">
+        <v>48654</v>
+      </c>
+      <c r="M76" t="n">
+        <v>48836</v>
+      </c>
+      <c r="N76" t="n">
+        <v>49018</v>
+      </c>
+      <c r="O76" t="n">
+        <v>49132</v>
+      </c>
+      <c r="P76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S76" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V76" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W76" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X76"/>
+  <dimension ref="A1:X78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6816,13 +6816,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>49470</v>
+        <v>49960</v>
       </c>
       <c r="C76" t="n">
         <v>50247</v>
       </c>
       <c r="D76" t="n">
-        <v>49461</v>
+        <v>49933</v>
       </c>
       <c r="E76" t="n">
         <v>50118</v>
@@ -6834,7 +6834,7 @@
         <v>0.0297</v>
       </c>
       <c r="H76" t="n">
-        <v>786</v>
+        <v>314</v>
       </c>
       <c r="I76" t="n">
         <v>48142</v>
@@ -6892,6 +6892,170 @@
         </is>
       </c>
       <c r="X76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>50180</v>
+      </c>
+      <c r="C77" t="n">
+        <v>50265</v>
+      </c>
+      <c r="D77" t="n">
+        <v>49720</v>
+      </c>
+      <c r="E77" t="n">
+        <v>50051</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-67</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="H77" t="n">
+        <v>545</v>
+      </c>
+      <c r="I77" t="n">
+        <v>49619</v>
+      </c>
+      <c r="J77" t="n">
+        <v>49818</v>
+      </c>
+      <c r="K77" t="n">
+        <v>49961</v>
+      </c>
+      <c r="L77" t="n">
+        <v>50104</v>
+      </c>
+      <c r="M77" t="n">
+        <v>50275</v>
+      </c>
+      <c r="N77" t="n">
+        <v>50446</v>
+      </c>
+      <c r="O77" t="n">
+        <v>50561</v>
+      </c>
+      <c r="P77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S77" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U77" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V77" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W77" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>50109</v>
+      </c>
+      <c r="C78" t="n">
+        <v>50265</v>
+      </c>
+      <c r="D78" t="n">
+        <v>49950</v>
+      </c>
+      <c r="E78" t="n">
+        <v>50051</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>315</v>
+      </c>
+      <c r="I78" t="n">
+        <v>49175</v>
+      </c>
+      <c r="J78" t="n">
+        <v>49535.25</v>
+      </c>
+      <c r="K78" t="n">
+        <v>49778.5</v>
+      </c>
+      <c r="L78" t="n">
+        <v>50021.75</v>
+      </c>
+      <c r="M78" t="n">
+        <v>50323.5</v>
+      </c>
+      <c r="N78" t="n">
+        <v>50625.25</v>
+      </c>
+      <c r="O78" t="n">
+        <v>50810</v>
+      </c>
+      <c r="P78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S78" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U78" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V78" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W78" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X78"/>
+  <dimension ref="A1:X79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6986,25 +6986,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>50109</v>
+        <v>50050</v>
       </c>
       <c r="C78" t="n">
-        <v>50265</v>
+        <v>50117</v>
       </c>
       <c r="D78" t="n">
-        <v>49950</v>
+        <v>49253</v>
       </c>
       <c r="E78" t="n">
-        <v>50051</v>
+        <v>49593</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>-458</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0</v>
+        <v>-0.0092</v>
       </c>
       <c r="H78" t="n">
-        <v>315</v>
+        <v>864</v>
       </c>
       <c r="I78" t="n">
         <v>49175</v>
@@ -7030,15 +7030,19 @@
       <c r="P78" s="6" t="n">
         <v/>
       </c>
-      <c r="Q78" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R78" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S78" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S78" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T78" s="8" t="n">
@@ -7055,7 +7059,93 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr"/>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>49946</v>
+      </c>
+      <c r="C79" t="n">
+        <v>49946</v>
+      </c>
+      <c r="D79" t="n">
+        <v>49253</v>
+      </c>
+      <c r="E79" t="n">
+        <v>49593</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>693</v>
+      </c>
+      <c r="I79" t="n">
+        <v>48389</v>
+      </c>
+      <c r="J79" t="n">
+        <v>48683</v>
+      </c>
+      <c r="K79" t="n">
+        <v>49161</v>
+      </c>
+      <c r="L79" t="n">
+        <v>49639</v>
+      </c>
+      <c r="M79" t="n">
+        <v>50025</v>
+      </c>
+      <c r="N79" t="n">
+        <v>50411</v>
+      </c>
+      <c r="O79" t="n">
+        <v>50981</v>
+      </c>
+      <c r="P79" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q79" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R79" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S79" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U79" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V79" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W79" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -7072,25 +7072,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>49946</v>
+        <v>49480</v>
       </c>
       <c r="C79" t="n">
-        <v>49946</v>
+        <v>49692</v>
       </c>
       <c r="D79" t="n">
-        <v>49253</v>
+        <v>49333</v>
       </c>
       <c r="E79" t="n">
-        <v>49593</v>
+        <v>49349</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>-244</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0</v>
+        <v>-0.0049</v>
       </c>
       <c r="H79" t="n">
-        <v>693</v>
+        <v>359</v>
       </c>
       <c r="I79" t="n">
         <v>48389</v>
@@ -7119,12 +7119,14 @@
       <c r="Q79" s="6" t="n">
         <v/>
       </c>
-      <c r="R79" s="6" t="n">
-        <v/>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S79" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T79" s="8" t="n">
@@ -7143,7 +7145,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X79"/>
+  <dimension ref="A1:X80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7078,19 +7078,19 @@
         <v>49692</v>
       </c>
       <c r="D79" t="n">
-        <v>49333</v>
+        <v>48413</v>
       </c>
       <c r="E79" t="n">
-        <v>49349</v>
+        <v>48705</v>
       </c>
       <c r="F79" t="n">
-        <v>-244</v>
+        <v>-888</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0179</v>
       </c>
       <c r="H79" t="n">
-        <v>359</v>
+        <v>1279</v>
       </c>
       <c r="I79" t="n">
         <v>48389</v>
@@ -7116,12 +7116,14 @@
       <c r="P79" s="6" t="n">
         <v/>
       </c>
-      <c r="Q79" s="6" t="n">
-        <v/>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S79" s="10" t="inlineStr">
@@ -7145,7 +7147,89 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>49122</v>
+      </c>
+      <c r="C80" t="n">
+        <v>49226</v>
+      </c>
+      <c r="D80" t="n">
+        <v>48413</v>
+      </c>
+      <c r="E80" t="n">
+        <v>48705</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>813</v>
+      </c>
+      <c r="I80" t="n">
+        <v>47134</v>
+      </c>
+      <c r="J80" t="n">
+        <v>47252.25</v>
+      </c>
+      <c r="K80" t="n">
+        <v>48065.5</v>
+      </c>
+      <c r="L80" t="n">
+        <v>48878.75</v>
+      </c>
+      <c r="M80" t="n">
+        <v>49344.5</v>
+      </c>
+      <c r="N80" t="n">
+        <v>49810.25</v>
+      </c>
+      <c r="O80" t="n">
+        <v>50971</v>
+      </c>
+      <c r="P80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S80" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W80" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X80"/>
+  <dimension ref="A1:X81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7158,25 +7158,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>49122</v>
+        <v>48975</v>
       </c>
       <c r="C80" t="n">
-        <v>49226</v>
+        <v>49594</v>
       </c>
       <c r="D80" t="n">
-        <v>48413</v>
+        <v>48881</v>
       </c>
       <c r="E80" t="n">
-        <v>48705</v>
+        <v>48946</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0</v>
+        <v>0.0049</v>
       </c>
       <c r="H80" t="n">
-        <v>813</v>
+        <v>713</v>
       </c>
       <c r="I80" t="n">
         <v>47134</v>
@@ -7208,26 +7208,112 @@
       <c r="R80" s="6" t="n">
         <v/>
       </c>
-      <c r="S80" s="10" t="inlineStr">
+      <c r="S80" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W80" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>49275</v>
+      </c>
+      <c r="C81" t="n">
+        <v>49422</v>
+      </c>
+      <c r="D81" t="n">
+        <v>48881</v>
+      </c>
+      <c r="E81" t="n">
+        <v>48946</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>541</v>
+      </c>
+      <c r="I81" t="n">
+        <v>48168</v>
+      </c>
+      <c r="J81" t="n">
+        <v>48087.25</v>
+      </c>
+      <c r="K81" t="n">
+        <v>48589.5</v>
+      </c>
+      <c r="L81" t="n">
+        <v>49091.75</v>
+      </c>
+      <c r="M81" t="n">
+        <v>49302.5</v>
+      </c>
+      <c r="N81" t="n">
+        <v>49513.25</v>
+      </c>
+      <c r="O81" t="n">
+        <v>50307</v>
+      </c>
+      <c r="P81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S81" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W80" s="9" t="inlineStr">
+      <c r="T81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U81" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V81" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W81" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X81"/>
+  <dimension ref="A1:X82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7242,25 +7242,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>49275</v>
+        <v>48606</v>
       </c>
       <c r="C81" t="n">
-        <v>49422</v>
+        <v>48873</v>
       </c>
       <c r="D81" t="n">
-        <v>48881</v>
+        <v>48240</v>
       </c>
       <c r="E81" t="n">
-        <v>48946</v>
+        <v>48755</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>-191</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0</v>
+        <v>-0.0039</v>
       </c>
       <c r="H81" t="n">
-        <v>541</v>
+        <v>633</v>
       </c>
       <c r="I81" t="n">
         <v>48168</v>
@@ -7289,18 +7289,18 @@
       <c r="Q81" s="6" t="n">
         <v/>
       </c>
-      <c r="R81" s="6" t="n">
-        <v/>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S81" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="n">
+        <v/>
       </c>
       <c r="U81" s="8" t="n">
         <v/>
@@ -7315,9 +7315,89 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>48433</v>
+      </c>
+      <c r="C82" t="n">
+        <v>48873</v>
+      </c>
+      <c r="D82" t="n">
+        <v>48357</v>
+      </c>
+      <c r="E82" t="n">
+        <v>48755</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>516</v>
+      </c>
+      <c r="I82" t="n">
+        <v>47607</v>
+      </c>
+      <c r="J82" t="n">
+        <v>48221.25</v>
+      </c>
+      <c r="K82" t="n">
+        <v>48438.5</v>
+      </c>
+      <c r="L82" t="n">
+        <v>48655.75</v>
+      </c>
+      <c r="M82" t="n">
+        <v>49071.5</v>
+      </c>
+      <c r="N82" t="n">
+        <v>49487.25</v>
+      </c>
+      <c r="O82" t="n">
+        <v>49506</v>
+      </c>
+      <c r="P82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S82" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U82" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V82" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W82" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X82"/>
+  <dimension ref="A1:X83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7245,22 +7245,22 @@
         <v>48606</v>
       </c>
       <c r="C81" t="n">
-        <v>48873</v>
+        <v>48793</v>
       </c>
       <c r="D81" t="n">
         <v>48240</v>
       </c>
       <c r="E81" t="n">
-        <v>48755</v>
+        <v>48400</v>
       </c>
       <c r="F81" t="n">
-        <v>-191</v>
+        <v>-546</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0112</v>
       </c>
       <c r="H81" t="n">
-        <v>633</v>
+        <v>553</v>
       </c>
       <c r="I81" t="n">
         <v>48168</v>
@@ -7326,78 +7326,172 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>48433</v>
+        <v>48789</v>
       </c>
       <c r="C82" t="n">
-        <v>48873</v>
+        <v>49200</v>
       </c>
       <c r="D82" t="n">
-        <v>48357</v>
+        <v>47850</v>
       </c>
       <c r="E82" t="n">
-        <v>48755</v>
+        <v>47945</v>
       </c>
       <c r="F82" t="n">
+        <v>-455</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-0.0094</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1350</v>
+      </c>
+      <c r="I82" t="n">
+        <v>47687</v>
+      </c>
+      <c r="J82" t="n">
+        <v>47788.75</v>
+      </c>
+      <c r="K82" t="n">
+        <v>48123.5</v>
+      </c>
+      <c r="L82" t="n">
+        <v>48458.25</v>
+      </c>
+      <c r="M82" t="n">
+        <v>48676.5</v>
+      </c>
+      <c r="N82" t="n">
+        <v>48894.75</v>
+      </c>
+      <c r="O82" t="n">
+        <v>49346</v>
+      </c>
+      <c r="P82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S82" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V82" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W82" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>48801</v>
+      </c>
+      <c r="C83" t="n">
+        <v>49000</v>
+      </c>
+      <c r="D83" t="n">
+        <v>47850</v>
+      </c>
+      <c r="E83" t="n">
+        <v>47945</v>
+      </c>
+      <c r="F83" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="5" t="n">
+      <c r="G83" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H82" t="n">
-        <v>516</v>
-      </c>
-      <c r="I82" t="n">
-        <v>47607</v>
-      </c>
-      <c r="J82" t="n">
-        <v>48221.25</v>
-      </c>
-      <c r="K82" t="n">
-        <v>48438.5</v>
-      </c>
-      <c r="L82" t="n">
-        <v>48655.75</v>
-      </c>
-      <c r="M82" t="n">
-        <v>49071.5</v>
-      </c>
-      <c r="N82" t="n">
-        <v>49487.25</v>
-      </c>
-      <c r="O82" t="n">
-        <v>49506</v>
-      </c>
-      <c r="P82" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q82" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R82" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S82" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U82" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V82" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W82" s="9" t="inlineStr">
+      <c r="H83" t="n">
+        <v>1150</v>
+      </c>
+      <c r="I83" t="n">
+        <v>46500</v>
+      </c>
+      <c r="J83" t="n">
+        <v>46305</v>
+      </c>
+      <c r="K83" t="n">
+        <v>47270</v>
+      </c>
+      <c r="L83" t="n">
+        <v>48235</v>
+      </c>
+      <c r="M83" t="n">
+        <v>48620</v>
+      </c>
+      <c r="N83" t="n">
+        <v>49005</v>
+      </c>
+      <c r="O83" t="n">
+        <v>50550</v>
+      </c>
+      <c r="P83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S83" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U83" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V83" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W83" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr"/>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -7245,22 +7245,22 @@
         <v>48606</v>
       </c>
       <c r="C81" t="n">
-        <v>48793</v>
+        <v>48873</v>
       </c>
       <c r="D81" t="n">
         <v>48240</v>
       </c>
       <c r="E81" t="n">
-        <v>48400</v>
+        <v>48755</v>
       </c>
       <c r="F81" t="n">
-        <v>-546</v>
+        <v>-191</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0112</v>
+        <v>-0.0039</v>
       </c>
       <c r="H81" t="n">
-        <v>553</v>
+        <v>633</v>
       </c>
       <c r="I81" t="n">
         <v>48168</v>
@@ -7338,34 +7338,34 @@
         <v>47945</v>
       </c>
       <c r="F82" t="n">
-        <v>-455</v>
+        <v>-810</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0166</v>
       </c>
       <c r="H82" t="n">
         <v>1350</v>
       </c>
       <c r="I82" t="n">
-        <v>47687</v>
+        <v>47607</v>
       </c>
       <c r="J82" t="n">
-        <v>47788.75</v>
+        <v>48221.25</v>
       </c>
       <c r="K82" t="n">
-        <v>48123.5</v>
+        <v>48438.5</v>
       </c>
       <c r="L82" t="n">
-        <v>48458.25</v>
+        <v>48655.75</v>
       </c>
       <c r="M82" t="n">
-        <v>48676.5</v>
+        <v>49071.5</v>
       </c>
       <c r="N82" t="n">
-        <v>48894.75</v>
+        <v>49487.25</v>
       </c>
       <c r="O82" t="n">
-        <v>49346</v>
+        <v>49506</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7390,22 +7390,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U82" s="8" t="n">
+        <v/>
       </c>
       <c r="V82" s="8" t="n">
         <v/>
       </c>
-      <c r="W82" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W82" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -7482,16 +7480,12 @@
       <c r="V83" s="8" t="n">
         <v/>
       </c>
-      <c r="W83" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W83" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X83"/>
+  <dimension ref="A1:X84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7414,25 +7414,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>48801</v>
+        <v>47716</v>
       </c>
       <c r="C83" t="n">
-        <v>49000</v>
+        <v>47720</v>
       </c>
       <c r="D83" t="n">
-        <v>47850</v>
+        <v>46456</v>
       </c>
       <c r="E83" t="n">
-        <v>47945</v>
+        <v>47366</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>-579</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0</v>
+        <v>-0.0121</v>
       </c>
       <c r="H83" t="n">
-        <v>1150</v>
+        <v>1264</v>
       </c>
       <c r="I83" t="n">
         <v>46500</v>
@@ -7455,24 +7455,26 @@
       <c r="O83" t="n">
         <v>50550</v>
       </c>
-      <c r="P83" s="6" t="n">
-        <v/>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q83" s="6" t="n">
         <v/>
       </c>
-      <c r="R83" s="6" t="n">
-        <v/>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S83" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="n">
+        <v/>
       </c>
       <c r="U83" s="8" t="n">
         <v/>
@@ -7486,6 +7488,86 @@
         </is>
       </c>
       <c r="X83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>46926</v>
+      </c>
+      <c r="C84" t="n">
+        <v>47417</v>
+      </c>
+      <c r="D84" t="n">
+        <v>46456</v>
+      </c>
+      <c r="E84" t="n">
+        <v>47366</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>961</v>
+      </c>
+      <c r="I84" t="n">
+        <v>45192</v>
+      </c>
+      <c r="J84" t="n">
+        <v>46241</v>
+      </c>
+      <c r="K84" t="n">
+        <v>46734</v>
+      </c>
+      <c r="L84" t="n">
+        <v>47227</v>
+      </c>
+      <c r="M84" t="n">
+        <v>47998</v>
+      </c>
+      <c r="N84" t="n">
+        <v>48769</v>
+      </c>
+      <c r="O84" t="n">
+        <v>48984</v>
+      </c>
+      <c r="P84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S84" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U84" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V84" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W84" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -7496,25 +7496,25 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>46926</v>
+        <v>47228</v>
       </c>
       <c r="C84" t="n">
-        <v>47417</v>
+        <v>47634</v>
       </c>
       <c r="D84" t="n">
-        <v>46456</v>
+        <v>47140</v>
       </c>
       <c r="E84" t="n">
-        <v>47366</v>
+        <v>47242</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>-124</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0</v>
+        <v>-0.0026</v>
       </c>
       <c r="H84" t="n">
-        <v>961</v>
+        <v>494</v>
       </c>
       <c r="I84" t="n">
         <v>45192</v>
@@ -7543,10 +7543,8 @@
       <c r="Q84" s="6" t="n">
         <v/>
       </c>
-      <c r="R84" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R84" s="6" t="n">
+        <v/>
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
@@ -7567,7 +7565,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr"/>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X84"/>
+  <dimension ref="A1:X85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7571,6 +7571,90 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>47269</v>
+      </c>
+      <c r="C85" t="n">
+        <v>47380</v>
+      </c>
+      <c r="D85" t="n">
+        <v>46107</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46140</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-1102</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-0.0233</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1273</v>
+      </c>
+      <c r="I85" t="n">
+        <v>46646</v>
+      </c>
+      <c r="J85" t="n">
+        <v>46675.5</v>
+      </c>
+      <c r="K85" t="n">
+        <v>46995</v>
+      </c>
+      <c r="L85" t="n">
+        <v>47314.5</v>
+      </c>
+      <c r="M85" t="n">
+        <v>47489</v>
+      </c>
+      <c r="N85" t="n">
+        <v>47663.5</v>
+      </c>
+      <c r="O85" t="n">
+        <v>48128</v>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S85" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U85" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V85" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W85" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X85"/>
+  <dimension ref="A1:X86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7578,25 +7578,25 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>47269</v>
+        <v>46627</v>
       </c>
       <c r="C85" t="n">
-        <v>47380</v>
+        <v>47033</v>
       </c>
       <c r="D85" t="n">
-        <v>46107</v>
+        <v>46390</v>
       </c>
       <c r="E85" t="n">
-        <v>46140</v>
+        <v>46691</v>
       </c>
       <c r="F85" t="n">
-        <v>-1102</v>
+        <v>-551</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.0233</v>
+        <v>-0.0117</v>
       </c>
       <c r="H85" t="n">
-        <v>1273</v>
+        <v>643</v>
       </c>
       <c r="I85" t="n">
         <v>46646</v>
@@ -7621,14 +7621,14 @@
       </c>
       <c r="P85" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q85" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7654,6 +7654,90 @@
         </is>
       </c>
       <c r="X85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>46842</v>
+      </c>
+      <c r="C86" t="n">
+        <v>47033</v>
+      </c>
+      <c r="D86" t="n">
+        <v>46497</v>
+      </c>
+      <c r="E86" t="n">
+        <v>46691</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>536</v>
+      </c>
+      <c r="I86" t="n">
+        <v>45747</v>
+      </c>
+      <c r="J86" t="n">
+        <v>46037.75</v>
+      </c>
+      <c r="K86" t="n">
+        <v>46369.5</v>
+      </c>
+      <c r="L86" t="n">
+        <v>46701.25</v>
+      </c>
+      <c r="M86" t="n">
+        <v>47012.5</v>
+      </c>
+      <c r="N86" t="n">
+        <v>47323.75</v>
+      </c>
+      <c r="O86" t="n">
+        <v>47676</v>
+      </c>
+      <c r="P86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S86" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U86" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V86" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W86" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X86"/>
+  <dimension ref="A1:X87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7662,25 +7662,25 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>46842</v>
+        <v>46434</v>
       </c>
       <c r="C86" t="n">
-        <v>47033</v>
+        <v>46920</v>
       </c>
       <c r="D86" t="n">
-        <v>46497</v>
+        <v>46162</v>
       </c>
       <c r="E86" t="n">
-        <v>46691</v>
+        <v>46384</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>-307</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0</v>
+        <v>-0.0066</v>
       </c>
       <c r="H86" t="n">
-        <v>536</v>
+        <v>758</v>
       </c>
       <c r="I86" t="n">
         <v>45747</v>
@@ -7709,18 +7709,18 @@
       <c r="Q86" s="6" t="n">
         <v/>
       </c>
-      <c r="R86" s="6" t="n">
-        <v/>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S86" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="n">
+        <v/>
       </c>
       <c r="U86" s="8" t="n">
         <v/>
@@ -7733,9 +7733,91 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>46490</v>
+      </c>
+      <c r="C87" t="n">
+        <v>47098</v>
+      </c>
+      <c r="D87" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E87" t="n">
+        <v>46975</v>
+      </c>
+      <c r="F87" t="n">
+        <v>591</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="H87" t="n">
+        <v>962</v>
+      </c>
+      <c r="I87" t="n">
+        <v>45404</v>
+      </c>
+      <c r="J87" t="n">
+        <v>45547.5</v>
+      </c>
+      <c r="K87" t="n">
+        <v>46005</v>
+      </c>
+      <c r="L87" t="n">
+        <v>46462.5</v>
+      </c>
+      <c r="M87" t="n">
+        <v>46763</v>
+      </c>
+      <c r="N87" t="n">
+        <v>47063.5</v>
+      </c>
+      <c r="O87" t="n">
+        <v>47678</v>
+      </c>
+      <c r="P87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S87" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U87" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W87" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -7665,22 +7665,22 @@
         <v>46434</v>
       </c>
       <c r="C86" t="n">
-        <v>46920</v>
+        <v>47098</v>
       </c>
       <c r="D86" t="n">
-        <v>46162</v>
+        <v>46136</v>
       </c>
       <c r="E86" t="n">
-        <v>46384</v>
+        <v>46975</v>
       </c>
       <c r="F86" t="n">
-        <v>-307</v>
+        <v>284</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.0066</v>
+        <v>0.0061</v>
       </c>
       <c r="H86" t="n">
-        <v>758</v>
+        <v>962</v>
       </c>
       <c r="I86" t="n">
         <v>45747</v>
@@ -7711,17 +7711,19 @@
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S86" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S86" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T86" s="8" t="n">
-        <v/>
-      </c>
       <c r="U86" s="8" t="n">
         <v/>
       </c>
@@ -7733,7 +7735,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr"/>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7754,58 +7760,58 @@
         <v>46975</v>
       </c>
       <c r="F87" t="n">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>962</v>
       </c>
       <c r="I87" t="n">
-        <v>45404</v>
+        <v>45174</v>
       </c>
       <c r="J87" t="n">
-        <v>45547.5</v>
+        <v>46192</v>
       </c>
       <c r="K87" t="n">
-        <v>46005</v>
+        <v>46494</v>
       </c>
       <c r="L87" t="n">
-        <v>46462.5</v>
+        <v>46796</v>
       </c>
       <c r="M87" t="n">
-        <v>46763</v>
+        <v>47456</v>
       </c>
       <c r="N87" t="n">
-        <v>47063.5</v>
+        <v>48116</v>
       </c>
       <c r="O87" t="n">
-        <v>47678</v>
+        <v>48060</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
       </c>
-      <c r="Q87" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R87" s="6" t="n">
-        <v/>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S87" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U87" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U87" s="8" t="n">
+        <v/>
       </c>
       <c r="V87" s="8" t="n">
         <v/>
@@ -7815,11 +7821,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X87"/>
+  <dimension ref="A1:X88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7748,25 +7748,25 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>46490</v>
+        <v>47388</v>
       </c>
       <c r="C87" t="n">
-        <v>47098</v>
+        <v>47555</v>
       </c>
       <c r="D87" t="n">
-        <v>46136</v>
+        <v>46872</v>
       </c>
       <c r="E87" t="n">
-        <v>46975</v>
+        <v>47482</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0</v>
+        <v>0.0108</v>
       </c>
       <c r="H87" t="n">
-        <v>962</v>
+        <v>683</v>
       </c>
       <c r="I87" t="n">
         <v>45174</v>
@@ -7792,36 +7792,122 @@
       <c r="P87" s="6" t="n">
         <v/>
       </c>
-      <c r="Q87" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R87" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R87" s="6" t="n">
+        <v/>
       </c>
       <c r="S87" s="7" t="inlineStr">
         <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W87" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>46991</v>
+      </c>
+      <c r="C88" t="n">
+        <v>47555</v>
+      </c>
+      <c r="D88" t="n">
+        <v>46983</v>
+      </c>
+      <c r="E88" t="n">
+        <v>47482</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>572</v>
+      </c>
+      <c r="I88" t="n">
+        <v>46189</v>
+      </c>
+      <c r="J88" t="n">
+        <v>46933.25</v>
+      </c>
+      <c r="K88" t="n">
+        <v>47140.5</v>
+      </c>
+      <c r="L88" t="n">
+        <v>47347.75</v>
+      </c>
+      <c r="M88" t="n">
+        <v>47823.5</v>
+      </c>
+      <c r="N88" t="n">
+        <v>48299.25</v>
+      </c>
+      <c r="O88" t="n">
+        <v>48238</v>
+      </c>
+      <c r="P88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S88" s="7" t="inlineStr">
+        <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W87" s="11" t="inlineStr">
+      <c r="T88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W88" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr"/>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X88"/>
+  <dimension ref="A1:X89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7832,25 +7832,25 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>46991</v>
+        <v>47164</v>
       </c>
       <c r="C88" t="n">
-        <v>47555</v>
+        <v>47337</v>
       </c>
       <c r="D88" t="n">
-        <v>46983</v>
+        <v>45523</v>
       </c>
       <c r="E88" t="n">
-        <v>47482</v>
+        <v>45654</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>-1828</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0</v>
+        <v>-0.0385</v>
       </c>
       <c r="H88" t="n">
-        <v>572</v>
+        <v>1814</v>
       </c>
       <c r="I88" t="n">
         <v>46189</v>
@@ -7873,20 +7873,24 @@
       <c r="O88" t="n">
         <v>48238</v>
       </c>
-      <c r="P88" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q88" s="6" t="n">
-        <v/>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S88" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S88" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T88" s="8" t="n">
@@ -7903,11 +7907,85 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C89" t="n">
+        <v>46399</v>
+      </c>
+      <c r="D89" t="n">
+        <v>45523</v>
+      </c>
+      <c r="E89" t="n">
+        <v>45654</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>876</v>
+      </c>
+      <c r="I89" t="n">
+        <v>43709</v>
+      </c>
+      <c r="J89" t="n">
+        <v>43452</v>
+      </c>
+      <c r="K89" t="n">
+        <v>44747</v>
+      </c>
+      <c r="L89" t="n">
+        <v>46042</v>
+      </c>
+      <c r="M89" t="n">
+        <v>46561</v>
+      </c>
+      <c r="N89" t="n">
+        <v>47080</v>
+      </c>
+      <c r="O89" t="n">
+        <v>49151</v>
+      </c>
+      <c r="P89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S89" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W89" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -7838,19 +7838,19 @@
         <v>47337</v>
       </c>
       <c r="D88" t="n">
-        <v>45523</v>
+        <v>46217</v>
       </c>
       <c r="E88" t="n">
-        <v>45654</v>
+        <v>46272</v>
       </c>
       <c r="F88" t="n">
-        <v>-1828</v>
+        <v>-1210</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-0.0385</v>
+        <v>-0.0255</v>
       </c>
       <c r="H88" t="n">
-        <v>1814</v>
+        <v>1120</v>
       </c>
       <c r="I88" t="n">
         <v>46189</v>
@@ -7928,34 +7928,34 @@
         <v>45654</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>-618</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0</v>
+        <v>-0.0134</v>
       </c>
       <c r="H89" t="n">
         <v>876</v>
       </c>
       <c r="I89" t="n">
-        <v>43709</v>
+        <v>45097</v>
       </c>
       <c r="J89" t="n">
-        <v>43452</v>
+        <v>44899.5</v>
       </c>
       <c r="K89" t="n">
-        <v>44747</v>
+        <v>45712</v>
       </c>
       <c r="L89" t="n">
-        <v>46042</v>
+        <v>46524.5</v>
       </c>
       <c r="M89" t="n">
-        <v>46561</v>
+        <v>46832</v>
       </c>
       <c r="N89" t="n">
-        <v>47080</v>
+        <v>47139.5</v>
       </c>
       <c r="O89" t="n">
-        <v>49151</v>
+        <v>48457</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7963,12 +7963,14 @@
       <c r="Q89" s="6" t="n">
         <v/>
       </c>
-      <c r="R89" s="6" t="n">
-        <v/>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S89" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T89" s="8" t="n">

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X89"/>
+  <dimension ref="A1:X90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7989,6 +7989,88 @@
       </c>
       <c r="X89" t="inlineStr"/>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C90" t="n">
+        <v>46399</v>
+      </c>
+      <c r="D90" t="n">
+        <v>45523</v>
+      </c>
+      <c r="E90" t="n">
+        <v>45654</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>876</v>
+      </c>
+      <c r="I90" t="n">
+        <v>44647</v>
+      </c>
+      <c r="J90" t="n">
+        <v>44624.5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>45216</v>
+      </c>
+      <c r="L90" t="n">
+        <v>45807.5</v>
+      </c>
+      <c r="M90" t="n">
+        <v>46092</v>
+      </c>
+      <c r="N90" t="n">
+        <v>46376.5</v>
+      </c>
+      <c r="O90" t="n">
+        <v>47275</v>
+      </c>
+      <c r="P90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S90" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V90" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W90" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X90"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7996,25 +7996,25 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>46270</v>
+        <v>46505</v>
       </c>
       <c r="C90" t="n">
-        <v>46399</v>
+        <v>47000</v>
       </c>
       <c r="D90" t="n">
-        <v>45523</v>
+        <v>46006</v>
       </c>
       <c r="E90" t="n">
-        <v>45654</v>
+        <v>46880</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1226</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0</v>
+        <v>0.0269</v>
       </c>
       <c r="H90" t="n">
-        <v>876</v>
+        <v>994</v>
       </c>
       <c r="I90" t="n">
         <v>44647</v>
@@ -8046,9 +8046,9 @@
       <c r="R90" s="6" t="n">
         <v/>
       </c>
-      <c r="S90" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S90" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T90" s="8" t="inlineStr">
@@ -8061,15 +8061,99 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V90" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W90" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V90" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W90" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>46080</v>
+      </c>
+      <c r="C91" t="n">
+        <v>47000</v>
+      </c>
+      <c r="D91" t="n">
+        <v>46006</v>
+      </c>
+      <c r="E91" t="n">
+        <v>46880</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>994</v>
+      </c>
+      <c r="I91" t="n">
+        <v>45012</v>
+      </c>
+      <c r="J91" t="n">
+        <v>46074.5</v>
+      </c>
+      <c r="K91" t="n">
+        <v>46383</v>
+      </c>
+      <c r="L91" t="n">
+        <v>46691.5</v>
+      </c>
+      <c r="M91" t="n">
+        <v>47377</v>
+      </c>
+      <c r="N91" t="n">
+        <v>48062.5</v>
+      </c>
+      <c r="O91" t="n">
+        <v>47994</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W91" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -8080,25 +8080,25 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>46080</v>
+        <v>46971</v>
       </c>
       <c r="C91" t="n">
-        <v>47000</v>
+        <v>47607</v>
       </c>
       <c r="D91" t="n">
-        <v>46006</v>
+        <v>46892</v>
       </c>
       <c r="E91" t="n">
-        <v>46880</v>
+        <v>47121</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="H91" t="n">
-        <v>994</v>
+        <v>715</v>
       </c>
       <c r="I91" t="n">
         <v>45012</v>
@@ -8124,23 +8124,21 @@
       <c r="P91" s="6" t="n">
         <v/>
       </c>
-      <c r="Q91" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R91" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="n">
+        <v/>
       </c>
       <c r="S91" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U91" s="8" t="n">
         <v/>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X91"/>
+  <dimension ref="A1:X93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8153,6 +8153,170 @@
       </c>
       <c r="X91" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>47187</v>
+      </c>
+      <c r="C92" t="n">
+        <v>47218</v>
+      </c>
+      <c r="D92" t="n">
+        <v>45850</v>
+      </c>
+      <c r="E92" t="n">
+        <v>45926</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-1195</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-0.0254</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1368</v>
+      </c>
+      <c r="I92" t="n">
+        <v>46177</v>
+      </c>
+      <c r="J92" t="n">
+        <v>46341.75</v>
+      </c>
+      <c r="K92" t="n">
+        <v>46763.5</v>
+      </c>
+      <c r="L92" t="n">
+        <v>47185.25</v>
+      </c>
+      <c r="M92" t="n">
+        <v>47478.5</v>
+      </c>
+      <c r="N92" t="n">
+        <v>47771.75</v>
+      </c>
+      <c r="O92" t="n">
+        <v>48322</v>
+      </c>
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q92" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R92" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S92" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T92" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U92" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V92" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W92" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>46400</v>
+      </c>
+      <c r="C93" t="n">
+        <v>46637</v>
+      </c>
+      <c r="D93" t="n">
+        <v>45850</v>
+      </c>
+      <c r="E93" t="n">
+        <v>45926</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>787</v>
+      </c>
+      <c r="I93" t="n">
+        <v>44482</v>
+      </c>
+      <c r="J93" t="n">
+        <v>44254</v>
+      </c>
+      <c r="K93" t="n">
+        <v>45242</v>
+      </c>
+      <c r="L93" t="n">
+        <v>46230</v>
+      </c>
+      <c r="M93" t="n">
+        <v>46610</v>
+      </c>
+      <c r="N93" t="n">
+        <v>46990</v>
+      </c>
+      <c r="O93" t="n">
+        <v>48586</v>
+      </c>
+      <c r="P93" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q93" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R93" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S93" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T93" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U93" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V93" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W93" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/TX_daily.xlsx
+++ b/three_gate/analysis/TX_daily.xlsx
@@ -8244,25 +8244,25 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>46400</v>
+        <v>45410</v>
       </c>
       <c r="C93" t="n">
-        <v>46637</v>
+        <v>45597</v>
       </c>
       <c r="D93" t="n">
-        <v>45850</v>
+        <v>44908</v>
       </c>
       <c r="E93" t="n">
-        <v>45926</v>
+        <v>45301</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>-625</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0</v>
+        <v>-0.0136</v>
       </c>
       <c r="H93" t="n">
-        <v>787</v>
+        <v>689</v>
       </c>
       <c r="I93" t="n">
         <v>44482</v>
@@ -8291,18 +8291,18 @@
       <c r="Q93" s="6" t="n">
         <v/>
       </c>
-      <c r="R93" s="6" t="n">
-        <v/>
+      <c r="R93" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S93" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T93" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T93" s="8" t="n">
+        <v/>
       </c>
       <c r="U93" s="8" t="n">
         <v/>
